--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF9504BD-B3F8-4E61-A780-9639EFB4F224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24B83BA-4431-405D-8304-F26C82C015F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -1210,9 +1210,6 @@
     <t>Via Belfiore, 16/C</t>
   </si>
   <si>
-    <t>Corso Castefidardo, 22</t>
-  </si>
-  <si>
     <t>Via Cernaia, 18</t>
   </si>
   <si>
@@ -1252,9 +1249,6 @@
     <t>Largo IV Marzo, 17/C</t>
   </si>
   <si>
-    <t>Corso Sebastoboli, 241</t>
-  </si>
-  <si>
     <t>Lingotto</t>
   </si>
   <si>
@@ -1639,9 +1633,6 @@
     <t>Via Giuseppe Baretti,18/E</t>
   </si>
   <si>
-    <t>Strada Comunale Val San Martino, 4</t>
-  </si>
-  <si>
     <t>Quadrilatero</t>
   </si>
   <si>
@@ -2116,9 +2107,6 @@
     <t>Via Sant'Ottavio, 52/D</t>
   </si>
   <si>
-    <t>Corso Vittorio Emanuele II, 24/bis</t>
-  </si>
-  <si>
     <t>Via Claudio Luigi Berthollet, 30</t>
   </si>
   <si>
@@ -2443,9 +2431,6 @@
     <t>romana</t>
   </si>
   <si>
-    <t>Via Principe d'Acaja, 65/D</t>
-  </si>
-  <si>
     <t>Piazza Benefica</t>
   </si>
   <si>
@@ -2852,6 +2837,21 @@
   </si>
   <si>
     <t>Isabella Brandino</t>
+  </si>
+  <si>
+    <t>Strada Val S. Martino, 4</t>
+  </si>
+  <si>
+    <t>Corso Castelfidardo, 22</t>
+  </si>
+  <si>
+    <t>Corso Sebastopoli, 241</t>
+  </si>
+  <si>
+    <t>Corso Vittorio Emanuele II, 24</t>
+  </si>
+  <si>
+    <t>Via Principi d'Acaja, 65/D</t>
   </si>
 </sst>
 </file>
@@ -3747,7 +3747,7 @@
         <v>120</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
@@ -3858,13 +3858,13 @@
     </row>
     <row r="7" spans="1:45" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>13</v>
@@ -3885,16 +3885,16 @@
         <v>11</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="K7" s="29" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="L7" s="23" t="s">
         <v>19</v>
       </c>
       <c r="M7" s="27" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="N7" s="24" t="s">
         <v>0</v>
@@ -3987,22 +3987,22 @@
         <v>1</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="E8" s="34" t="s">
         <v>239</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="H8" s="34" t="s">
         <v>193</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="J8" s="33">
         <v>99</v>
@@ -4011,13 +4011,13 @@
         <v>304</v>
       </c>
       <c r="L8" s="33" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="O8" s="35">
         <v>1</v>
@@ -4115,7 +4115,7 @@
         <v>277</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="F9" s="31" t="s">
         <v>289</v>
@@ -4262,10 +4262,10 @@
         <v>130</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O10" s="35">
         <v>1</v>
@@ -4381,16 +4381,16 @@
         <v>99</v>
       </c>
       <c r="K11" s="36" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="L11" s="36" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="N11" s="37" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="O11" s="38"/>
       <c r="P11" s="36"/>
@@ -4483,22 +4483,22 @@
         <v>1</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>596</v>
+        <v>593</v>
       </c>
       <c r="E12" s="41" t="s">
         <v>281</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H12" s="41" t="s">
         <v>193</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>597</v>
+        <v>594</v>
       </c>
       <c r="J12" s="40">
         <v>99</v>
@@ -4507,10 +4507,10 @@
         <v>304</v>
       </c>
       <c r="L12" s="40" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="M12" s="41" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="N12" s="41"/>
       <c r="O12" s="42"/>
@@ -4613,7 +4613,7 @@
         <v>288</v>
       </c>
       <c r="G13" s="34" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H13" s="34" t="s">
         <v>193</v>
@@ -4625,7 +4625,7 @@
         <v>1</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="L13" s="33" t="s">
         <v>105</v>
@@ -4634,7 +4634,7 @@
         <v>105</v>
       </c>
       <c r="N13" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O13" s="35">
         <v>1</v>
@@ -4731,13 +4731,13 @@
         <v>1</v>
       </c>
       <c r="D14" s="37" t="s">
-        <v>593</v>
+        <v>590</v>
       </c>
       <c r="E14" s="37" t="s">
         <v>281</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>595</v>
+        <v>592</v>
       </c>
       <c r="G14" s="37" t="s">
         <v>90</v>
@@ -4746,7 +4746,7 @@
         <v>193</v>
       </c>
       <c r="I14" s="36" t="s">
-        <v>594</v>
+        <v>591</v>
       </c>
       <c r="J14" s="36">
         <v>2</v>
@@ -4761,7 +4761,7 @@
         <v>198</v>
       </c>
       <c r="N14" s="37" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="O14" s="38"/>
       <c r="P14" s="36"/>
@@ -4854,24 +4854,24 @@
         <v>2</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="E15" s="31" t="s">
         <v>281</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="31" t="s">
         <v>193</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="J15" s="30"/>
       <c r="K15" s="30" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L15" s="30"/>
       <c r="M15" s="31"/>
@@ -4969,13 +4969,13 @@
         <v>2</v>
       </c>
       <c r="D16" s="19" t="s">
+        <v>763</v>
+      </c>
+      <c r="E16" s="19" t="s">
         <v>767</v>
       </c>
-      <c r="E16" s="19" t="s">
-        <v>771</v>
-      </c>
       <c r="F16" s="19" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="G16" s="19" t="s">
         <v>84</v>
@@ -4984,7 +4984,7 @@
         <v>193</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="J16" s="20">
         <v>1</v>
@@ -4996,7 +4996,7 @@
         <v>305</v>
       </c>
       <c r="M16" s="19" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="N16" s="19"/>
       <c r="O16" s="18"/>
@@ -5090,22 +5090,22 @@
         <v>2</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="E17" s="34" t="s">
         <v>238</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>667</v>
+        <v>663</v>
       </c>
       <c r="G17" s="34" t="s">
         <v>105</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="I17" s="33" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="J17" s="33">
         <v>99</v>
@@ -5117,10 +5117,10 @@
         <v>47</v>
       </c>
       <c r="M17" s="34" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="N17" s="34" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="O17" s="35">
         <v>1</v>
@@ -5215,35 +5215,35 @@
         <v>2</v>
       </c>
       <c r="D18" s="37" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="E18" s="37" t="s">
         <v>238</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="G18" s="37" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="H18" s="37" t="s">
         <v>193</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="J18" s="36"/>
       <c r="K18" s="36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L18" s="36">
         <v>45</v>
       </c>
       <c r="M18" s="37" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="N18" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O18" s="38"/>
       <c r="P18" s="36"/>
@@ -5336,13 +5336,13 @@
         <v>2</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="G19" s="19" t="s">
         <v>85</v>
@@ -5351,16 +5351,16 @@
         <v>193</v>
       </c>
       <c r="I19" s="20" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J19" s="20">
         <v>6</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="M19" s="19" t="s">
         <v>198</v>
@@ -5481,10 +5481,10 @@
         <v>296</v>
       </c>
       <c r="L20" s="20" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="M20" s="19" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="N20" s="19"/>
       <c r="O20" s="18"/>
@@ -5578,13 +5578,13 @@
         <v>2</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E21" s="19" t="s">
         <v>238</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G21" s="19" t="s">
         <v>72</v>
@@ -5593,7 +5593,7 @@
         <v>193</v>
       </c>
       <c r="I21" s="20" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="J21" s="20">
         <v>4</v>
@@ -5605,7 +5605,7 @@
         <v>305</v>
       </c>
       <c r="M21" s="19" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="N21" s="19"/>
       <c r="O21" s="18"/>
@@ -5726,7 +5726,7 @@
         <v>305</v>
       </c>
       <c r="M22" s="19" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="N22" s="19"/>
       <c r="O22" s="18"/>
@@ -5965,13 +5965,13 @@
         <v>295</v>
       </c>
       <c r="L24" s="36" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="M24" s="37" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="N24" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O24" s="38"/>
       <c r="P24" s="36"/>
@@ -6064,22 +6064,22 @@
         <v>2</v>
       </c>
       <c r="D25" s="37" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="E25" s="37" t="s">
         <v>281</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>612</v>
+        <v>609</v>
       </c>
       <c r="G25" s="37" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="H25" s="37" t="s">
         <v>193</v>
       </c>
       <c r="I25" s="36" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="J25" s="36">
         <v>99</v>
@@ -6088,13 +6088,13 @@
         <v>294</v>
       </c>
       <c r="L25" s="36" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="M25" s="37" t="s">
         <v>198</v>
       </c>
       <c r="N25" s="37" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="O25" s="38"/>
       <c r="P25" s="36"/>
@@ -6187,22 +6187,22 @@
         <v>2</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E26" s="37" t="s">
         <v>238</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="H26" s="37" t="s">
         <v>193</v>
       </c>
       <c r="I26" s="36" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="J26" s="36">
         <v>7</v>
@@ -6211,13 +6211,13 @@
         <v>296</v>
       </c>
       <c r="L26" s="36" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="M26" s="37" t="s">
         <v>198</v>
       </c>
       <c r="N26" s="37" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O26" s="38"/>
       <c r="P26" s="36"/>
@@ -6430,13 +6430,13 @@
         <v>2</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="E28" s="19" t="s">
         <v>239</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>634</v>
+        <v>631</v>
       </c>
       <c r="G28" s="19" t="s">
         <v>139</v>
@@ -6445,16 +6445,16 @@
         <v>193</v>
       </c>
       <c r="I28" s="20" t="s">
-        <v>635</v>
+        <v>632</v>
       </c>
       <c r="J28" s="20">
         <v>6</v>
       </c>
       <c r="K28" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>687</v>
+        <v>683</v>
       </c>
       <c r="M28" s="19" t="s">
         <v>198</v>
@@ -6551,13 +6551,13 @@
         <v>2</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>638</v>
+        <v>635</v>
       </c>
       <c r="E29" s="34" t="s">
         <v>281</v>
       </c>
       <c r="F29" s="34" t="s">
-        <v>639</v>
+        <v>636</v>
       </c>
       <c r="G29" s="34" t="s">
         <v>90</v>
@@ -6566,7 +6566,7 @@
         <v>193</v>
       </c>
       <c r="I29" s="33" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="J29" s="33">
         <v>2</v>
@@ -6575,13 +6575,13 @@
         <v>295</v>
       </c>
       <c r="L29" s="33" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="M29" s="34" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="N29" s="34" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="O29" s="35">
         <v>1</v>
@@ -6701,10 +6701,10 @@
       </c>
       <c r="L30" s="36"/>
       <c r="M30" s="37" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="N30" s="37" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="O30" s="38"/>
       <c r="P30" s="36"/>
@@ -6797,13 +6797,13 @@
         <v>2</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="E31" s="37" t="s">
         <v>238</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>568</v>
+        <v>565</v>
       </c>
       <c r="G31" s="37" t="s">
         <v>84</v>
@@ -6812,7 +6812,7 @@
         <v>193</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J31" s="36">
         <v>1</v>
@@ -6821,13 +6821,13 @@
         <v>304</v>
       </c>
       <c r="L31" s="36" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O31" s="38"/>
       <c r="P31" s="36"/>
@@ -6950,7 +6950,7 @@
         <v>249</v>
       </c>
       <c r="N32" s="37" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="O32" s="38"/>
       <c r="P32" s="36"/>
@@ -7043,11 +7043,11 @@
         <v>2</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="E33" s="34"/>
       <c r="F33" s="34" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="G33" s="34" t="s">
         <v>90</v>
@@ -7056,16 +7056,16 @@
         <v>193</v>
       </c>
       <c r="I33" s="33" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="J33" s="33"/>
       <c r="K33" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L33" s="33"/>
       <c r="M33" s="34"/>
       <c r="N33" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O33" s="35">
         <v>1</v>
@@ -7162,13 +7162,13 @@
         <v>2</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="E34" s="19" t="s">
         <v>281</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="G34" s="19" t="s">
         <v>84</v>
@@ -7177,17 +7177,17 @@
         <v>193</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="J34" s="20"/>
       <c r="K34" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L34" s="20">
         <v>75</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="N34" s="19"/>
       <c r="O34" s="18"/>
@@ -7296,7 +7296,7 @@
         <v>193</v>
       </c>
       <c r="I35" s="20" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J35" s="20">
         <v>2</v>
@@ -7305,10 +7305,10 @@
         <v>302</v>
       </c>
       <c r="L35" s="20" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="N35" s="19"/>
       <c r="O35" s="18"/>
@@ -7402,13 +7402,13 @@
         <v>3</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="E36" s="37" t="s">
         <v>238</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="G36" s="37" t="s">
         <v>103</v>
@@ -7417,7 +7417,7 @@
         <v>193</v>
       </c>
       <c r="I36" s="36" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="J36" s="36">
         <v>7</v>
@@ -7426,13 +7426,13 @@
         <v>302</v>
       </c>
       <c r="L36" s="36" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="M36" s="37" t="s">
         <v>198</v>
       </c>
       <c r="N36" s="37" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="O36" s="38"/>
       <c r="P36" s="36"/>
@@ -7549,13 +7549,13 @@
         <v>294</v>
       </c>
       <c r="L37" s="33" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="M37" s="34" t="s">
         <v>308</v>
       </c>
       <c r="N37" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O37" s="35">
         <v>1</v>
@@ -7652,22 +7652,22 @@
         <v>3</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="E38" s="37" t="s">
         <v>237</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>600</v>
+        <v>597</v>
       </c>
       <c r="G38" s="37" t="s">
         <v>105</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="I38" s="36" t="s">
-        <v>601</v>
+        <v>598</v>
       </c>
       <c r="J38" s="36">
         <v>99</v>
@@ -7679,10 +7679,10 @@
         <v>65</v>
       </c>
       <c r="M38" s="37" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="N38" s="37" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="O38" s="38"/>
       <c r="P38" s="36"/>
@@ -7775,34 +7775,34 @@
         <v>3</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="E39" s="19" t="s">
         <v>237</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H39" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="J39" s="20">
         <v>99</v>
       </c>
       <c r="K39" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L39" s="20" t="s">
         <v>309</v>
       </c>
       <c r="M39" s="19" t="s">
-        <v>686</v>
+        <v>682</v>
       </c>
       <c r="N39" s="19"/>
       <c r="O39" s="18"/>
@@ -7896,13 +7896,13 @@
         <v>3</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="G40" s="37" t="s">
         <v>84</v>
@@ -7911,7 +7911,7 @@
         <v>193</v>
       </c>
       <c r="I40" s="36" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="J40" s="36">
         <v>1</v>
@@ -7923,10 +7923,10 @@
         <v>50</v>
       </c>
       <c r="M40" s="37" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="N40" s="37" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="O40" s="38"/>
       <c r="P40" s="36"/>
@@ -8019,13 +8019,13 @@
         <v>3</v>
       </c>
       <c r="D41" s="34" t="s">
-        <v>706</v>
+        <v>702</v>
       </c>
       <c r="E41" s="34" t="s">
         <v>237</v>
       </c>
       <c r="F41" s="34" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="G41" s="34" t="s">
         <v>104</v>
@@ -8034,7 +8034,7 @@
         <v>193</v>
       </c>
       <c r="I41" s="33" t="s">
-        <v>707</v>
+        <v>703</v>
       </c>
       <c r="J41" s="33">
         <v>2</v>
@@ -8043,13 +8043,13 @@
         <v>296</v>
       </c>
       <c r="L41" s="33" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="M41" s="34" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="N41" s="34" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="O41" s="35">
         <v>1</v>
@@ -8165,13 +8165,13 @@
         <v>4</v>
       </c>
       <c r="K42" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L42" s="20">
         <v>40</v>
       </c>
       <c r="M42" s="19" t="s">
-        <v>605</v>
+        <v>602</v>
       </c>
       <c r="N42" s="19"/>
       <c r="O42" s="18"/>
@@ -8286,7 +8286,7 @@
         <v>99</v>
       </c>
       <c r="K43" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L43" s="20">
         <v>30</v>
@@ -8392,7 +8392,7 @@
         <v>242</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="G44" s="19" t="s">
         <v>72</v>
@@ -8407,13 +8407,13 @@
         <v>4</v>
       </c>
       <c r="K44" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L44" s="20">
         <v>38</v>
       </c>
       <c r="M44" s="19" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="N44" s="19"/>
       <c r="O44" s="18"/>
@@ -8507,13 +8507,13 @@
         <v>3</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E45" s="19" t="s">
         <v>237</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G45" s="19" t="s">
         <v>109</v>
@@ -8522,19 +8522,19 @@
         <v>193</v>
       </c>
       <c r="I45" s="20" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="J45" s="20">
         <v>99</v>
       </c>
       <c r="K45" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L45" s="20">
         <v>25</v>
       </c>
       <c r="M45" s="19" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="N45" s="19"/>
       <c r="O45" s="18"/>
@@ -8628,13 +8628,13 @@
         <v>3</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="E46" s="19" t="s">
         <v>237</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>84</v>
@@ -8643,13 +8643,13 @@
         <v>193</v>
       </c>
       <c r="I46" s="20" t="s">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="J46" s="20">
         <v>1</v>
       </c>
       <c r="K46" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L46" s="20">
         <v>35</v>
@@ -8764,7 +8764,7 @@
         <v>193</v>
       </c>
       <c r="I47" s="33" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J47" s="33">
         <v>2</v>
@@ -8773,13 +8773,13 @@
         <v>302</v>
       </c>
       <c r="L47" s="33" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="M47" s="34" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="N47" s="34" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="O47" s="35">
         <v>1</v>
@@ -8901,10 +8901,10 @@
         <v>307</v>
       </c>
       <c r="M48" s="37" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="N48" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O48" s="38"/>
       <c r="P48" s="36"/>
@@ -9027,7 +9027,7 @@
         <v>306</v>
       </c>
       <c r="N49" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O49" s="38"/>
       <c r="P49" s="36"/>
@@ -9150,7 +9150,7 @@
         <v>198</v>
       </c>
       <c r="N50" s="34" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="O50" s="35">
         <v>1</v>
@@ -9245,22 +9245,22 @@
         <v>3</v>
       </c>
       <c r="D51" s="37" t="s">
-        <v>615</v>
+        <v>612</v>
       </c>
       <c r="E51" s="37" t="s">
         <v>237</v>
       </c>
       <c r="F51" s="37" t="s">
-        <v>616</v>
+        <v>613</v>
       </c>
       <c r="G51" s="37" t="s">
-        <v>618</v>
+        <v>615</v>
       </c>
       <c r="H51" s="37" t="s">
         <v>193</v>
       </c>
       <c r="I51" s="36" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="J51" s="36">
         <v>99</v>
@@ -9269,13 +9269,13 @@
         <v>302</v>
       </c>
       <c r="L51" s="36" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="M51" s="37" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="N51" s="37" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O51" s="38"/>
       <c r="P51" s="36"/>
@@ -9380,7 +9380,7 @@
         <v>193</v>
       </c>
       <c r="I52" s="20" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J52" s="20">
         <v>2</v>
@@ -9389,10 +9389,10 @@
         <v>301</v>
       </c>
       <c r="L52" s="20" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="M52" s="19" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="N52" s="19"/>
       <c r="O52" s="18"/>
@@ -9516,7 +9516,7 @@
         <v>306</v>
       </c>
       <c r="N53" s="37" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="O53" s="38"/>
       <c r="P53" s="36"/>
@@ -9609,22 +9609,22 @@
         <v>3</v>
       </c>
       <c r="D54" s="37" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E54" s="37" t="s">
         <v>238</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>506</v>
+        <v>906</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="H54" s="37" t="s">
         <v>193</v>
       </c>
       <c r="I54" s="36" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="J54" s="36">
         <v>7</v>
@@ -9639,7 +9639,7 @@
         <v>268</v>
       </c>
       <c r="N54" s="37" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="O54" s="38"/>
       <c r="P54" s="36"/>
@@ -9732,13 +9732,13 @@
         <v>3</v>
       </c>
       <c r="D55" s="41" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="E55" s="41" t="s">
         <v>238</v>
       </c>
       <c r="F55" s="41" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="G55" s="41" t="s">
         <v>105</v>
@@ -9747,7 +9747,7 @@
         <v>193</v>
       </c>
       <c r="I55" s="40" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="J55" s="40">
         <v>99</v>
@@ -9756,10 +9756,10 @@
         <v>296</v>
       </c>
       <c r="L55" s="40" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="M55" s="41" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="N55" s="41"/>
       <c r="O55" s="42"/>
@@ -9853,13 +9853,13 @@
         <v>3</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="E56" s="34" t="s">
         <v>237</v>
       </c>
       <c r="F56" s="34" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="G56" s="34" t="s">
         <v>111</v>
@@ -9868,11 +9868,11 @@
         <v>193</v>
       </c>
       <c r="I56" s="33" t="s">
-        <v>874</v>
+        <v>869</v>
       </c>
       <c r="J56" s="33"/>
       <c r="K56" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L56" s="33">
         <v>38</v>
@@ -9881,7 +9881,7 @@
         <v>198</v>
       </c>
       <c r="N56" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O56" s="35">
         <v>1</v>
@@ -9999,7 +9999,7 @@
         <v>2</v>
       </c>
       <c r="K57" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L57" s="20" t="s">
         <v>309</v>
@@ -10099,13 +10099,13 @@
         <v>3</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="E58" s="34" t="s">
         <v>238</v>
       </c>
       <c r="F58" s="34" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="G58" s="34" t="s">
         <v>90</v>
@@ -10114,18 +10114,18 @@
         <v>193</v>
       </c>
       <c r="I58" s="33" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="J58" s="33">
         <v>2</v>
       </c>
       <c r="K58" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L58" s="33"/>
       <c r="M58" s="34"/>
       <c r="N58" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O58" s="35">
         <v>1</v>
@@ -10252,7 +10252,7 @@
         <v>250</v>
       </c>
       <c r="N59" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O59" s="35">
         <v>1</v>
@@ -10349,13 +10349,13 @@
         <v>5</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="E60" s="19" t="s">
         <v>240</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="G60" s="19" t="s">
         <v>102</v>
@@ -10364,7 +10364,7 @@
         <v>193</v>
       </c>
       <c r="I60" s="20" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="J60" s="20">
         <v>5</v>
@@ -10376,7 +10376,7 @@
         <v>309</v>
       </c>
       <c r="M60" s="19" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="N60" s="19"/>
       <c r="O60" s="18"/>
@@ -10470,13 +10470,13 @@
         <v>5</v>
       </c>
       <c r="D61" s="34" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="E61" s="34" t="s">
         <v>240</v>
       </c>
       <c r="F61" s="34" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="G61" s="34" t="s">
         <v>72</v>
@@ -10485,18 +10485,18 @@
         <v>193</v>
       </c>
       <c r="I61" s="33" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="J61" s="33">
         <v>4</v>
       </c>
       <c r="K61" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L61" s="33"/>
       <c r="M61" s="34"/>
       <c r="N61" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O61" s="35">
         <v>1</v>
@@ -10593,13 +10593,13 @@
         <v>5</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="E62" s="19" t="s">
         <v>240</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="G62" s="19" t="s">
         <v>102</v>
@@ -10608,19 +10608,19 @@
         <v>193</v>
       </c>
       <c r="I62" s="20" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J62" s="20">
         <v>5</v>
       </c>
       <c r="K62" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L62" s="20" t="s">
         <v>309</v>
       </c>
       <c r="M62" s="19" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="N62" s="19"/>
       <c r="O62" s="18"/>
@@ -10714,34 +10714,34 @@
         <v>5</v>
       </c>
       <c r="D63" s="19" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="E63" s="19" t="s">
         <v>240</v>
       </c>
       <c r="F63" s="19" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="H63" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I63" s="20" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="J63" s="20">
         <v>99</v>
       </c>
       <c r="K63" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L63" s="20">
         <v>30</v>
       </c>
       <c r="M63" s="19" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="N63" s="19"/>
       <c r="O63" s="18"/>
@@ -10835,13 +10835,13 @@
         <v>5</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="G64" s="19" t="s">
         <v>147</v>
@@ -10850,7 +10850,7 @@
         <v>193</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="J64" s="20">
         <v>99</v>
@@ -10862,7 +10862,7 @@
         <v>40</v>
       </c>
       <c r="M64" s="19" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="N64" s="19"/>
       <c r="O64" s="18"/>
@@ -10956,13 +10956,13 @@
         <v>5</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="G65" s="19" t="s">
         <v>105</v>
@@ -10971,7 +10971,7 @@
         <v>193</v>
       </c>
       <c r="I65" s="20" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="J65" s="20">
         <v>99</v>
@@ -10983,7 +10983,7 @@
         <v>40</v>
       </c>
       <c r="M65" s="19" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="N65" s="19"/>
       <c r="O65" s="18"/>
@@ -11077,13 +11077,13 @@
         <v>5</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="E66" s="37" t="s">
         <v>240</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>668</v>
+        <v>664</v>
       </c>
       <c r="G66" s="37" t="s">
         <v>84</v>
@@ -11092,7 +11092,7 @@
         <v>193</v>
       </c>
       <c r="I66" s="36" t="s">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="J66" s="36">
         <v>1</v>
@@ -11101,13 +11101,13 @@
         <v>296</v>
       </c>
       <c r="L66" s="36" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="M66" s="37" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="N66" s="37" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="O66" s="38"/>
       <c r="P66" s="36"/>
@@ -11221,16 +11221,16 @@
         <v>4</v>
       </c>
       <c r="K67" s="36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L67" s="36">
         <v>31</v>
       </c>
       <c r="M67" s="37" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="N67" s="37" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="O67" s="38"/>
       <c r="P67" s="36"/>
@@ -11338,7 +11338,7 @@
         <v>193</v>
       </c>
       <c r="I68" s="36" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="J68" s="36">
         <v>5</v>
@@ -11347,13 +11347,13 @@
         <v>302</v>
       </c>
       <c r="L68" s="36" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="M68" s="37" t="s">
         <v>198</v>
       </c>
       <c r="N68" s="37" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="O68" s="38"/>
       <c r="P68" s="36"/>
@@ -11446,13 +11446,13 @@
         <v>5</v>
       </c>
       <c r="D69" s="34" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="E69" s="34" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="F69" s="34" t="s">
-        <v>838</v>
+        <v>833</v>
       </c>
       <c r="G69" s="34" t="s">
         <v>72</v>
@@ -11461,20 +11461,20 @@
         <v>193</v>
       </c>
       <c r="I69" s="33" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="J69" s="33"/>
       <c r="K69" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L69" s="33">
         <v>45</v>
       </c>
       <c r="M69" s="34" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="N69" s="34" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="O69" s="35">
         <v>1</v>
@@ -11569,13 +11569,13 @@
         <v>5</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="E70" s="37" t="s">
         <v>240</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="G70" s="37" t="s">
         <v>139</v>
@@ -11584,7 +11584,7 @@
         <v>193</v>
       </c>
       <c r="I70" s="36" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J70" s="36">
         <v>1</v>
@@ -11593,13 +11593,13 @@
         <v>295</v>
       </c>
       <c r="L70" s="36" t="s">
-        <v>688</v>
+        <v>684</v>
       </c>
       <c r="M70" s="37" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="N70" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O70" s="38"/>
       <c r="P70" s="36"/>
@@ -11692,37 +11692,37 @@
         <v>5</v>
       </c>
       <c r="D71" s="34" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="E71" s="34" t="s">
         <v>240</v>
       </c>
       <c r="F71" s="34" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="G71" s="34" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="H71" s="34" t="s">
         <v>193</v>
       </c>
       <c r="I71" s="33" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="J71" s="33">
         <v>1</v>
       </c>
       <c r="K71" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L71" s="33">
         <v>35</v>
       </c>
       <c r="M71" s="34" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="N71" s="34" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="O71" s="35">
         <v>1</v>
@@ -11817,10 +11817,10 @@
         <v>5</v>
       </c>
       <c r="D72" s="34" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="E72" s="34" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="F72" s="34" t="s">
         <v>68</v>
@@ -11832,7 +11832,7 @@
         <v>193</v>
       </c>
       <c r="I72" s="33" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="J72" s="33">
         <v>2</v>
@@ -11844,10 +11844,10 @@
         <v>40</v>
       </c>
       <c r="M72" s="34" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="N72" s="34" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="O72" s="35">
         <v>1</v>
@@ -11957,13 +11957,13 @@
         <v>193</v>
       </c>
       <c r="I73" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J73" s="20">
         <v>99</v>
       </c>
       <c r="K73" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L73" s="20" t="s">
         <v>311</v>
@@ -12063,13 +12063,13 @@
         <v>6</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E74" s="19" t="s">
         <v>243</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G74" s="19" t="s">
         <v>72</v>
@@ -12078,19 +12078,19 @@
         <v>193</v>
       </c>
       <c r="I74" s="20" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="J74" s="20">
         <v>4</v>
       </c>
       <c r="K74" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L74" s="20" t="s">
         <v>310</v>
       </c>
       <c r="M74" s="19" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="N74" s="19"/>
       <c r="O74" s="18"/>
@@ -12184,22 +12184,22 @@
         <v>6</v>
       </c>
       <c r="D75" s="37" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E75" s="37" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="H75" s="37" t="s">
         <v>193</v>
       </c>
       <c r="I75" s="36" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="J75" s="36">
         <v>1</v>
@@ -12208,13 +12208,13 @@
         <v>296</v>
       </c>
       <c r="L75" s="36" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="M75" s="37" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="N75" s="37" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="O75" s="38"/>
       <c r="P75" s="36"/>
@@ -12328,7 +12328,7 @@
         <v>3</v>
       </c>
       <c r="K76" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L76" s="20" t="s">
         <v>311</v>
@@ -12428,13 +12428,13 @@
         <v>6</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E77" s="19" t="s">
         <v>244</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="G77" s="19" t="s">
         <v>90</v>
@@ -12443,7 +12443,7 @@
         <v>193</v>
       </c>
       <c r="I77" s="20" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="J77" s="20">
         <v>2</v>
@@ -12455,7 +12455,7 @@
         <v>305</v>
       </c>
       <c r="M77" s="19" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="N77" s="19"/>
       <c r="O77" s="18"/>
@@ -12549,13 +12549,13 @@
         <v>6</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>620</v>
+        <v>617</v>
       </c>
       <c r="E78" s="19" t="s">
         <v>244</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="G78" s="19" t="s">
         <v>84</v>
@@ -12564,7 +12564,7 @@
         <v>193</v>
       </c>
       <c r="I78" s="20" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="J78" s="20">
         <v>1</v>
@@ -12576,7 +12576,7 @@
         <v>305</v>
       </c>
       <c r="M78" s="19" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="N78" s="19"/>
       <c r="O78" s="18"/>
@@ -12694,13 +12694,13 @@
         <v>294</v>
       </c>
       <c r="L79" s="33" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="M79" s="34" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="N79" s="34" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="O79" s="35">
         <v>1</v>
@@ -12795,22 +12795,22 @@
         <v>6</v>
       </c>
       <c r="D80" s="34" t="s">
-        <v>583</v>
+        <v>580</v>
       </c>
       <c r="E80" s="34" t="s">
-        <v>584</v>
+        <v>581</v>
       </c>
       <c r="F80" s="34" t="s">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="G80" s="34" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="H80" s="34" t="s">
         <v>193</v>
       </c>
       <c r="I80" s="33" t="s">
-        <v>586</v>
+        <v>583</v>
       </c>
       <c r="J80" s="33">
         <v>1</v>
@@ -12825,7 +12825,7 @@
         <v>105</v>
       </c>
       <c r="N80" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O80" s="35">
         <v>1</v>
@@ -12946,13 +12946,13 @@
         <v>296</v>
       </c>
       <c r="L81" s="33" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="M81" s="34" t="s">
         <v>251</v>
       </c>
       <c r="N81" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O81" s="35">
         <v>1</v>
@@ -13047,22 +13047,22 @@
         <v>6</v>
       </c>
       <c r="D82" s="34" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="E82" s="34" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F82" s="34" t="s">
-        <v>627</v>
+        <v>624</v>
       </c>
       <c r="G82" s="34" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H82" s="34" t="s">
         <v>193</v>
       </c>
       <c r="I82" s="33" t="s">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="J82" s="33">
         <v>2</v>
@@ -13077,7 +13077,7 @@
         <v>105</v>
       </c>
       <c r="N82" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O82" s="35">
         <v>1</v>
@@ -13174,13 +13174,13 @@
         <v>6</v>
       </c>
       <c r="D83" s="34" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="E83" s="34" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="F83" s="34" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="G83" s="34" t="s">
         <v>146</v>
@@ -13189,7 +13189,7 @@
         <v>193</v>
       </c>
       <c r="I83" s="33" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="J83" s="33">
         <v>99</v>
@@ -13198,13 +13198,13 @@
         <v>301</v>
       </c>
       <c r="L83" s="33" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="M83" s="34" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="N83" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O83" s="35">
         <v>1</v>
@@ -13299,13 +13299,13 @@
         <v>6</v>
       </c>
       <c r="D84" s="34" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="E84" s="34" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="F84" s="34" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="G84" s="34" t="s">
         <v>90</v>
@@ -13314,22 +13314,22 @@
         <v>193</v>
       </c>
       <c r="I84" s="33" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="J84" s="33">
         <v>2</v>
       </c>
       <c r="K84" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L84" s="33">
         <v>45</v>
       </c>
       <c r="M84" s="34" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="N84" s="34" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="O84" s="35">
         <v>1</v>
@@ -13424,13 +13424,13 @@
         <v>6</v>
       </c>
       <c r="D85" s="37" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E85" s="37" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="G85" s="37" t="s">
         <v>72</v>
@@ -13439,7 +13439,7 @@
         <v>193</v>
       </c>
       <c r="I85" s="36" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="J85" s="36">
         <v>4</v>
@@ -13451,10 +13451,10 @@
         <v>310</v>
       </c>
       <c r="M85" s="37" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="N85" s="37" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O85" s="38"/>
       <c r="P85" s="36"/>
@@ -13544,22 +13544,22 @@
         <v>6</v>
       </c>
       <c r="D86" s="37" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="E86" s="37" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>631</v>
+        <v>628</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="H86" s="37" t="s">
         <v>193</v>
       </c>
       <c r="I86" s="36" t="s">
-        <v>632</v>
+        <v>629</v>
       </c>
       <c r="J86" s="36">
         <v>1</v>
@@ -13571,10 +13571,10 @@
         <v>310</v>
       </c>
       <c r="M86" s="37" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="N86" s="37" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O86" s="38"/>
       <c r="P86" s="36"/>
@@ -13688,13 +13688,13 @@
         <v>301</v>
       </c>
       <c r="L87" s="33" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="M87" s="34" t="s">
         <v>251</v>
       </c>
       <c r="N87" s="34" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="O87" s="35">
         <v>1</v>
@@ -13789,29 +13789,29 @@
         <v>6</v>
       </c>
       <c r="D88" s="34" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="E88" s="34" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="F88" s="34" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="G88" s="34"/>
       <c r="H88" s="34" t="s">
         <v>193</v>
       </c>
       <c r="I88" s="33" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="J88" s="33"/>
       <c r="K88" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L88" s="33"/>
       <c r="M88" s="34"/>
       <c r="N88" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O88" s="35">
         <v>1</v>
@@ -13923,7 +13923,7 @@
         <v>193</v>
       </c>
       <c r="I89" s="36" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="J89" s="36">
         <v>5</v>
@@ -13932,13 +13932,13 @@
         <v>295</v>
       </c>
       <c r="L89" s="36" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="M89" s="37" t="s">
         <v>198</v>
       </c>
       <c r="N89" s="37" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="O89" s="38"/>
       <c r="P89" s="36"/>
@@ -14031,13 +14031,13 @@
         <v>6</v>
       </c>
       <c r="D90" s="34" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="E90" s="34" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="F90" s="34" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="G90" s="34" t="s">
         <v>110</v>
@@ -14046,7 +14046,7 @@
         <v>193</v>
       </c>
       <c r="I90" s="33" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="J90" s="33">
         <v>1</v>
@@ -14058,10 +14058,10 @@
         <v>309</v>
       </c>
       <c r="M90" s="34" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="N90" s="34" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="O90" s="35">
         <v>1</v>
@@ -14177,7 +14177,7 @@
         <v>5</v>
       </c>
       <c r="K91" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L91" s="20" t="s">
         <v>311</v>
@@ -14277,13 +14277,13 @@
         <v>7</v>
       </c>
       <c r="D92" s="34" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="E92" s="34" t="s">
         <v>40</v>
       </c>
       <c r="F92" s="34" t="s">
-        <v>637</v>
+        <v>634</v>
       </c>
       <c r="G92" s="34" t="s">
         <v>105</v>
@@ -14304,10 +14304,10 @@
         <v>309</v>
       </c>
       <c r="M92" s="34" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="N92" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O92" s="35">
         <v>1</v>
@@ -14432,7 +14432,7 @@
         <v>313</v>
       </c>
       <c r="N93" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O93" s="35">
         <v>1</v>
@@ -14559,7 +14559,7 @@
         <v>313</v>
       </c>
       <c r="N94" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O94" s="35">
         <v>1</v>
@@ -14686,7 +14686,7 @@
         <v>313</v>
       </c>
       <c r="N95" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O95" s="35">
         <v>1</v>
@@ -14789,7 +14789,7 @@
         <v>40</v>
       </c>
       <c r="F96" s="37" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G96" s="37" t="s">
         <v>139</v>
@@ -14798,7 +14798,7 @@
         <v>193</v>
       </c>
       <c r="I96" s="36" t="s">
-        <v>630</v>
+        <v>627</v>
       </c>
       <c r="J96" s="36">
         <v>99</v>
@@ -14813,7 +14813,7 @@
         <v>271</v>
       </c>
       <c r="N96" s="37" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O96" s="38"/>
       <c r="P96" s="36"/>
@@ -14933,7 +14933,7 @@
         <v>271</v>
       </c>
       <c r="N97" s="37" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O97" s="38"/>
       <c r="P97" s="36"/>
@@ -15023,13 +15023,13 @@
         <v>7</v>
       </c>
       <c r="D98" s="34" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="E98" s="34" t="s">
         <v>40</v>
       </c>
       <c r="F98" s="34" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="G98" s="34" t="s">
         <v>72</v>
@@ -15038,22 +15038,22 @@
         <v>193</v>
       </c>
       <c r="I98" s="33" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="J98" s="33">
         <v>3</v>
       </c>
       <c r="K98" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L98" s="33">
         <v>28</v>
       </c>
       <c r="M98" s="34" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="N98" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O98" s="35">
         <v>1</v>
@@ -15151,7 +15151,7 @@
         <v>339</v>
       </c>
       <c r="E99" s="34" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="F99" s="34" t="s">
         <v>361</v>
@@ -15163,7 +15163,7 @@
         <v>193</v>
       </c>
       <c r="I99" s="33" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="J99" s="33">
         <v>1</v>
@@ -15178,7 +15178,7 @@
         <v>198</v>
       </c>
       <c r="N99" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O99" s="35">
         <v>1</v>
@@ -15273,34 +15273,34 @@
         <v>7</v>
       </c>
       <c r="D100" s="19" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="E100" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F100" s="19" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="H100" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I100" s="20" t="s">
-        <v>609</v>
+        <v>606</v>
       </c>
       <c r="J100" s="20">
         <v>99</v>
       </c>
       <c r="K100" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L100" s="20" t="s">
         <v>310</v>
       </c>
       <c r="M100" s="19" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="N100" s="19"/>
       <c r="O100" s="18"/>
@@ -15394,13 +15394,13 @@
         <v>7</v>
       </c>
       <c r="D101" s="37" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="E101" s="37" t="s">
         <v>40</v>
       </c>
       <c r="F101" s="37" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="G101" s="37" t="s">
         <v>72</v>
@@ -15409,7 +15409,7 @@
         <v>193</v>
       </c>
       <c r="I101" s="36" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="J101" s="36">
         <v>3</v>
@@ -15421,10 +15421,10 @@
         <v>30</v>
       </c>
       <c r="M101" s="37" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="N101" s="37" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="O101" s="38"/>
       <c r="P101" s="36"/>
@@ -15517,22 +15517,22 @@
         <v>7</v>
       </c>
       <c r="D102" s="37" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="E102" s="37" t="s">
         <v>40</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>567</v>
+        <v>564</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H102" s="37" t="s">
         <v>193</v>
       </c>
       <c r="I102" s="36" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="J102" s="36">
         <v>99</v>
@@ -15544,10 +15544,10 @@
         <v>309</v>
       </c>
       <c r="M102" s="37" t="s">
-        <v>575</v>
+        <v>572</v>
       </c>
       <c r="N102" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O102" s="38"/>
       <c r="P102" s="36"/>
@@ -15670,7 +15670,7 @@
         <v>252</v>
       </c>
       <c r="N103" s="37" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O103" s="38"/>
       <c r="P103" s="36"/>
@@ -15760,13 +15760,13 @@
         <v>1</v>
       </c>
       <c r="D104" s="34" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E104" s="34" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="F104" s="34" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="G104" s="34" t="s">
         <v>90</v>
@@ -15775,7 +15775,7 @@
         <v>193</v>
       </c>
       <c r="I104" s="33" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="J104" s="33">
         <v>2</v>
@@ -15787,10 +15787,10 @@
         <v>7</v>
       </c>
       <c r="M104" s="34" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="N104" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O104" s="35">
         <v>1</v>
@@ -15887,13 +15887,13 @@
         <v>1</v>
       </c>
       <c r="D105" s="34" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="E105" s="34" t="s">
         <v>69</v>
       </c>
       <c r="F105" s="34" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="G105" s="34" t="s">
         <v>90</v>
@@ -15902,22 +15902,22 @@
         <v>193</v>
       </c>
       <c r="I105" s="33" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="J105" s="33">
         <v>2</v>
       </c>
       <c r="K105" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L105" s="33">
         <v>5</v>
       </c>
       <c r="M105" s="34" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="N105" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O105" s="35">
         <v>1</v>
@@ -16014,13 +16014,13 @@
         <v>1</v>
       </c>
       <c r="D106" s="34" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="E106" s="34" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F106" s="34" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="G106" s="34" t="s">
         <v>84</v>
@@ -16029,7 +16029,7 @@
         <v>193</v>
       </c>
       <c r="I106" s="33" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J106" s="33">
         <v>1</v>
@@ -16044,7 +16044,7 @@
         <v>196</v>
       </c>
       <c r="N106" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O106" s="35">
         <v>1</v>
@@ -16141,13 +16141,13 @@
         <v>1</v>
       </c>
       <c r="D107" s="34" t="s">
-        <v>895</v>
+        <v>890</v>
       </c>
       <c r="E107" s="34" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="F107" s="34" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="G107" s="34" t="s">
         <v>146</v>
@@ -16156,7 +16156,7 @@
         <v>193</v>
       </c>
       <c r="I107" s="33" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="J107" s="33">
         <v>99</v>
@@ -16171,7 +16171,7 @@
         <v>196</v>
       </c>
       <c r="N107" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O107" s="35">
         <v>1</v>
@@ -16268,13 +16268,13 @@
         <v>1</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="E108" s="34" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="F108" s="34" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="G108" s="34" t="s">
         <v>105</v>
@@ -16283,7 +16283,7 @@
         <v>193</v>
       </c>
       <c r="I108" s="33" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="J108" s="33">
         <v>99</v>
@@ -16295,10 +16295,10 @@
         <v>9</v>
       </c>
       <c r="M108" s="34" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="N108" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O108" s="35">
         <v>1</v>
@@ -16404,7 +16404,7 @@
         <v>34</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H109" s="19" t="s">
         <v>193</v>
@@ -16416,7 +16416,7 @@
         <v>1</v>
       </c>
       <c r="K109" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L109" s="20" t="s">
         <v>298</v>
@@ -16537,7 +16537,7 @@
         <v>6</v>
       </c>
       <c r="K110" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L110" s="20" t="s">
         <v>298</v>
@@ -16643,7 +16643,7 @@
         <v>54</v>
       </c>
       <c r="F111" s="19" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G111" s="19" t="s">
         <v>84</v>
@@ -16652,13 +16652,13 @@
         <v>193</v>
       </c>
       <c r="I111" s="20" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="J111" s="20">
         <v>1</v>
       </c>
       <c r="K111" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L111" s="20" t="s">
         <v>298</v>
@@ -16761,7 +16761,7 @@
         <v>169</v>
       </c>
       <c r="E112" s="34" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="F112" s="34" t="s">
         <v>168</v>
@@ -16788,7 +16788,7 @@
         <v>196</v>
       </c>
       <c r="N112" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O112" s="35">
         <v>1</v>
@@ -17012,16 +17012,16 @@
         <v>61</v>
       </c>
       <c r="F114" s="31" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="G114" s="31" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="H114" s="31" t="s">
         <v>193</v>
       </c>
       <c r="I114" s="30" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="J114" s="30">
         <v>99</v>
@@ -17280,7 +17280,7 @@
         <v>196</v>
       </c>
       <c r="N116" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O116" s="35">
         <v>1</v>
@@ -17377,13 +17377,13 @@
         <v>1</v>
       </c>
       <c r="D117" s="34" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="E117" s="34" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="F117" s="34" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="G117" s="34" t="s">
         <v>90</v>
@@ -17392,7 +17392,7 @@
         <v>193</v>
       </c>
       <c r="I117" s="33" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="J117" s="33">
         <v>2</v>
@@ -17404,10 +17404,10 @@
         <v>9</v>
       </c>
       <c r="M117" s="34" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="N117" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O117" s="35">
         <v>1</v>
@@ -17504,34 +17504,34 @@
         <v>2</v>
       </c>
       <c r="D118" s="19" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="E118" s="19" t="s">
         <v>53</v>
       </c>
       <c r="F118" s="19" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="G118" s="19" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="H118" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I118" s="20" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="J118" s="20">
         <v>6</v>
       </c>
       <c r="K118" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L118" s="20">
         <v>20</v>
       </c>
       <c r="M118" s="19" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N118" s="19"/>
       <c r="O118" s="18"/>
@@ -17652,10 +17652,10 @@
         <v>307</v>
       </c>
       <c r="M119" s="37" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="N119" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O119" s="38"/>
       <c r="P119" s="36"/>
@@ -17748,35 +17748,35 @@
         <v>2</v>
       </c>
       <c r="D120" s="34" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="E120" s="34" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="F120" s="34" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="G120" s="34" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="H120" s="34" t="s">
         <v>193</v>
       </c>
       <c r="I120" s="33" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="J120" s="33"/>
       <c r="K120" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L120" s="33">
         <v>30</v>
       </c>
       <c r="M120" s="34" t="s">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="N120" s="34" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="O120" s="35">
         <v>1</v>
@@ -17871,13 +17871,13 @@
         <v>2</v>
       </c>
       <c r="D121" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="E121" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="F121" s="19" t="s">
         <v>413</v>
-      </c>
-      <c r="E121" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="F121" s="19" t="s">
-        <v>415</v>
       </c>
       <c r="G121" s="19" t="s">
         <v>84</v>
@@ -17886,7 +17886,7 @@
         <v>193</v>
       </c>
       <c r="I121" s="20" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="J121" s="20">
         <v>1</v>
@@ -17898,7 +17898,7 @@
         <v>314</v>
       </c>
       <c r="M121" s="19" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="N121" s="19"/>
       <c r="O121" s="18"/>
@@ -17992,13 +17992,13 @@
         <v>2</v>
       </c>
       <c r="D122" s="34" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="E122" s="34" t="s">
         <v>244</v>
       </c>
       <c r="F122" s="34" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="G122" s="34" t="s">
         <v>162</v>
@@ -18007,7 +18007,7 @@
         <v>193</v>
       </c>
       <c r="I122" s="33" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="J122" s="33">
         <v>1</v>
@@ -18016,13 +18016,13 @@
         <v>297</v>
       </c>
       <c r="L122" s="33" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="M122" s="34" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="N122" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O122" s="35">
         <v>1</v>
@@ -18117,13 +18117,13 @@
         <v>2</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E123" s="19" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F123" s="19" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G123" s="19" t="s">
         <v>72</v>
@@ -18132,19 +18132,19 @@
         <v>193</v>
       </c>
       <c r="I123" s="20" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J123" s="20">
         <v>4</v>
       </c>
       <c r="K123" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L123" s="20" t="s">
         <v>311</v>
       </c>
       <c r="M123" s="19" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="N123" s="19"/>
       <c r="O123" s="18"/>
@@ -18238,13 +18238,13 @@
         <v>2</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F124" s="19" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G124" s="19" t="s">
         <v>72</v>
@@ -18253,19 +18253,19 @@
         <v>193</v>
       </c>
       <c r="I124" s="20" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="J124" s="20">
         <v>4</v>
       </c>
       <c r="K124" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L124" s="20" t="s">
         <v>310</v>
       </c>
       <c r="M124" s="19" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="N124" s="19"/>
       <c r="O124" s="18"/>
@@ -18362,19 +18362,19 @@
         <v>206</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F125" s="19" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="H125" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I125" s="20" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="J125" s="20">
         <v>99</v>
@@ -18386,7 +18386,7 @@
         <v>310</v>
       </c>
       <c r="M125" s="19" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="N125" s="19"/>
       <c r="O125" s="18"/>
@@ -18483,7 +18483,7 @@
         <v>206</v>
       </c>
       <c r="E126" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F126" s="19" t="s">
         <v>286</v>
@@ -18507,7 +18507,7 @@
         <v>310</v>
       </c>
       <c r="M126" s="19" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="N126" s="19"/>
       <c r="O126" s="18"/>
@@ -18601,13 +18601,13 @@
         <v>2</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F127" s="19" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="G127" s="19" t="s">
         <v>72</v>
@@ -18616,19 +18616,19 @@
         <v>193</v>
       </c>
       <c r="I127" s="20" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="J127" s="20">
         <v>4</v>
       </c>
       <c r="K127" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L127" s="20" t="s">
         <v>314</v>
       </c>
       <c r="M127" s="19" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="N127" s="19"/>
       <c r="O127" s="18"/>
@@ -18728,7 +18728,7 @@
         <v>44</v>
       </c>
       <c r="F128" s="19" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G128" s="19" t="s">
         <v>72</v>
@@ -18737,7 +18737,7 @@
         <v>193</v>
       </c>
       <c r="I128" s="20" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="J128" s="20">
         <v>4</v>
@@ -18964,28 +18964,28 @@
         <v>2</v>
       </c>
       <c r="D130" s="19" t="s">
-        <v>890</v>
+        <v>885</v>
       </c>
       <c r="E130" s="19"/>
       <c r="F130" s="19" t="s">
-        <v>891</v>
+        <v>886</v>
       </c>
       <c r="G130" s="19"/>
       <c r="H130" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I130" s="20" t="s">
-        <v>892</v>
+        <v>887</v>
       </c>
       <c r="J130" s="20"/>
       <c r="K130" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L130" s="15">
         <v>22</v>
       </c>
       <c r="M130" s="39" t="s">
-        <v>893</v>
+        <v>888</v>
       </c>
       <c r="N130" s="39"/>
       <c r="O130" s="2"/>
@@ -19079,13 +19079,13 @@
         <v>2</v>
       </c>
       <c r="D131" s="37" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E131" s="37" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="F131" s="37" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="G131" s="37" t="s">
         <v>102</v>
@@ -19094,7 +19094,7 @@
         <v>193</v>
       </c>
       <c r="I131" s="36" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="J131" s="36">
         <v>5</v>
@@ -19106,10 +19106,10 @@
         <v>309</v>
       </c>
       <c r="M131" s="37" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N131" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O131" s="38"/>
       <c r="P131" s="36"/>
@@ -19202,13 +19202,13 @@
         <v>2</v>
       </c>
       <c r="D132" s="19" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E132" s="19" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="F132" s="19" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="G132" s="19" t="s">
         <v>72</v>
@@ -19217,19 +19217,19 @@
         <v>193</v>
       </c>
       <c r="I132" s="20" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="J132" s="20">
         <v>4</v>
       </c>
       <c r="K132" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L132" s="20" t="s">
         <v>310</v>
       </c>
       <c r="M132" s="19" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="N132" s="19"/>
       <c r="O132" s="18"/>
@@ -19323,13 +19323,13 @@
         <v>2</v>
       </c>
       <c r="D133" s="37" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E133" s="37" t="s">
         <v>282</v>
       </c>
       <c r="F133" s="37" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="G133" s="37" t="s">
         <v>147</v>
@@ -19338,7 +19338,7 @@
         <v>193</v>
       </c>
       <c r="I133" s="36" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="J133" s="36">
         <v>99</v>
@@ -19347,13 +19347,13 @@
         <v>293</v>
       </c>
       <c r="L133" s="36" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="M133" s="37" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="N133" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O133" s="38"/>
       <c r="P133" s="36"/>
@@ -19470,13 +19470,13 @@
         <v>297</v>
       </c>
       <c r="L134" s="33" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="M134" s="34" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="N134" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O134" s="35">
         <v>1</v>
@@ -19573,13 +19573,13 @@
         <v>3</v>
       </c>
       <c r="D135" s="31" t="s">
+        <v>552</v>
+      </c>
+      <c r="E135" s="31" t="s">
         <v>555</v>
       </c>
-      <c r="E135" s="31" t="s">
-        <v>558</v>
-      </c>
       <c r="F135" s="31" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="G135" s="31" t="s">
         <v>109</v>
@@ -19588,7 +19588,7 @@
         <v>193</v>
       </c>
       <c r="I135" s="30" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="J135" s="30">
         <v>1</v>
@@ -19696,22 +19696,22 @@
         <v>3</v>
       </c>
       <c r="D136" s="34" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="E136" s="34" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="F136" s="34" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="G136" s="34" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H136" s="34" t="s">
         <v>193</v>
       </c>
       <c r="I136" s="33" t="s">
-        <v>633</v>
+        <v>630</v>
       </c>
       <c r="J136" s="33">
         <v>1</v>
@@ -19726,7 +19726,7 @@
         <v>105</v>
       </c>
       <c r="N136" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O136" s="35">
         <v>1</v>
@@ -19853,7 +19853,7 @@
         <v>105</v>
       </c>
       <c r="N137" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O137" s="35">
         <v>1</v>
@@ -19950,13 +19950,13 @@
         <v>3</v>
       </c>
       <c r="D138" s="34" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="E138" s="34" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="F138" s="34" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="G138" s="34" t="s">
         <v>139</v>
@@ -19965,18 +19965,18 @@
         <v>193</v>
       </c>
       <c r="I138" s="33" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="J138" s="33">
         <v>1</v>
       </c>
       <c r="K138" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L138" s="33"/>
       <c r="M138" s="34"/>
       <c r="N138" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O138" s="35">
         <v>1</v>
@@ -20073,13 +20073,13 @@
         <v>3</v>
       </c>
       <c r="D139" s="34" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="E139" s="34" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="F139" s="34" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="G139" s="34" t="s">
         <v>139</v>
@@ -20088,7 +20088,7 @@
         <v>193</v>
       </c>
       <c r="I139" s="33" t="s">
-        <v>578</v>
+        <v>575</v>
       </c>
       <c r="J139" s="33">
         <v>1</v>
@@ -20103,7 +20103,7 @@
         <v>105</v>
       </c>
       <c r="N139" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O139" s="35">
         <v>1</v>
@@ -20230,7 +20230,7 @@
         <v>318</v>
       </c>
       <c r="N140" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O140" s="35">
         <v>1</v>
@@ -20450,13 +20450,13 @@
         <v>4</v>
       </c>
       <c r="D142" s="19" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E142" s="19" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F142" s="19" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="G142" s="19" t="s">
         <v>110</v>
@@ -20465,19 +20465,19 @@
         <v>193</v>
       </c>
       <c r="I142" s="20" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="J142" s="20">
         <v>1</v>
       </c>
       <c r="K142" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L142" s="20" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="M142" s="19" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="N142" s="19"/>
       <c r="O142" s="18"/>
@@ -20571,13 +20571,13 @@
         <v>4</v>
       </c>
       <c r="D143" s="37" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="E143" s="37" t="s">
         <v>37</v>
       </c>
       <c r="F143" s="37" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="G143" s="37" t="s">
         <v>72</v>
@@ -20586,7 +20586,7 @@
         <v>193</v>
       </c>
       <c r="I143" s="36" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J143" s="36">
         <v>3</v>
@@ -20598,10 +20598,10 @@
         <v>309</v>
       </c>
       <c r="M143" s="37" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="N143" s="37" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="O143" s="38"/>
       <c r="P143" s="36"/>
@@ -20694,22 +20694,22 @@
         <v>4</v>
       </c>
       <c r="D144" s="19" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="E144" s="19" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F144" s="19" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="G144" s="19" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="H144" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I144" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J144" s="20">
         <v>2</v>
@@ -20721,7 +20721,7 @@
         <v>311</v>
       </c>
       <c r="M144" s="19" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="N144" s="19"/>
       <c r="O144" s="18"/>
@@ -20815,13 +20815,13 @@
         <v>4</v>
       </c>
       <c r="D145" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="E145" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="F145" s="19" t="s">
         <v>417</v>
-      </c>
-      <c r="E145" s="19" t="s">
-        <v>418</v>
-      </c>
-      <c r="F145" s="19" t="s">
-        <v>419</v>
       </c>
       <c r="G145" s="19" t="s">
         <v>85</v>
@@ -20830,19 +20830,19 @@
         <v>193</v>
       </c>
       <c r="I145" s="20" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="J145" s="20">
         <v>6</v>
       </c>
       <c r="K145" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L145" s="20">
         <v>8</v>
       </c>
       <c r="M145" s="19" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="N145" s="19"/>
       <c r="O145" s="18"/>
@@ -20936,13 +20936,13 @@
         <v>4</v>
       </c>
       <c r="D146" s="37" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="E146" s="37" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F146" s="37" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="G146" s="37" t="s">
         <v>112</v>
@@ -20951,7 +20951,7 @@
         <v>193</v>
       </c>
       <c r="I146" s="36" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="J146" s="36">
         <v>3</v>
@@ -20963,10 +20963,10 @@
         <v>309</v>
       </c>
       <c r="M146" s="37" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="N146" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O146" s="38"/>
       <c r="P146" s="36"/>
@@ -21059,13 +21059,13 @@
         <v>4</v>
       </c>
       <c r="D147" s="37" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="E147" s="37" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="F147" s="37" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="G147" s="37" t="s">
         <v>84</v>
@@ -21074,7 +21074,7 @@
         <v>193</v>
       </c>
       <c r="I147" s="36" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="J147" s="36">
         <v>1</v>
@@ -21086,10 +21086,10 @@
         <v>311</v>
       </c>
       <c r="M147" s="37" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="N147" s="37" t="s">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="O147" s="38"/>
       <c r="P147" s="36"/>
@@ -21182,13 +21182,13 @@
         <v>4</v>
       </c>
       <c r="D148" s="19" t="s">
+        <v>553</v>
+      </c>
+      <c r="E148" s="19" t="s">
         <v>556</v>
       </c>
-      <c r="E148" s="19" t="s">
+      <c r="F148" s="19" t="s">
         <v>559</v>
-      </c>
-      <c r="F148" s="19" t="s">
-        <v>562</v>
       </c>
       <c r="G148" s="19" t="s">
         <v>90</v>
@@ -21197,7 +21197,7 @@
         <v>193</v>
       </c>
       <c r="I148" s="20" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="J148" s="20">
         <v>2</v>
@@ -21209,7 +21209,7 @@
         <v>311</v>
       </c>
       <c r="M148" s="19" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="N148" s="19"/>
       <c r="O148" s="18"/>
@@ -21303,13 +21303,13 @@
         <v>4</v>
       </c>
       <c r="D149" s="19" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E149" s="19" t="s">
         <v>30</v>
       </c>
       <c r="F149" s="19" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="G149" s="19" t="s">
         <v>103</v>
@@ -21318,7 +21318,7 @@
         <v>193</v>
       </c>
       <c r="I149" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J149" s="20">
         <v>7</v>
@@ -21330,7 +21330,7 @@
         <v>314</v>
       </c>
       <c r="M149" s="19" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="N149" s="19"/>
       <c r="O149" s="18"/>
@@ -21424,13 +21424,13 @@
         <v>4</v>
       </c>
       <c r="D150" s="19" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E150" s="19" t="s">
         <v>30</v>
       </c>
       <c r="F150" s="19" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="G150" s="19" t="s">
         <v>72</v>
@@ -21439,7 +21439,7 @@
         <v>193</v>
       </c>
       <c r="I150" s="20" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="J150" s="20">
         <v>4</v>
@@ -21451,7 +21451,7 @@
         <v>314</v>
       </c>
       <c r="M150" s="19" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="N150" s="19"/>
       <c r="O150" s="18"/>
@@ -21545,13 +21545,13 @@
         <v>4</v>
       </c>
       <c r="D151" s="19" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E151" s="19" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F151" s="19" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="G151" s="19" t="s">
         <v>84</v>
@@ -21560,19 +21560,19 @@
         <v>193</v>
       </c>
       <c r="I151" s="20" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="J151" s="20">
         <v>1</v>
       </c>
       <c r="K151" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L151" s="20">
         <v>15</v>
       </c>
       <c r="M151" s="19" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="N151" s="19"/>
       <c r="O151" s="18"/>
@@ -21666,13 +21666,13 @@
         <v>4</v>
       </c>
       <c r="D152" s="41" t="s">
+        <v>471</v>
+      </c>
+      <c r="E152" s="41" t="s">
+        <v>472</v>
+      </c>
+      <c r="F152" s="41" t="s">
         <v>473</v>
-      </c>
-      <c r="E152" s="41" t="s">
-        <v>474</v>
-      </c>
-      <c r="F152" s="41" t="s">
-        <v>475</v>
       </c>
       <c r="G152" s="41" t="s">
         <v>90</v>
@@ -21681,7 +21681,7 @@
         <v>193</v>
       </c>
       <c r="I152" s="40" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="J152" s="40">
         <v>2</v>
@@ -21693,10 +21693,10 @@
         <v>311</v>
       </c>
       <c r="M152" s="41" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="N152" s="41" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O152" s="42"/>
       <c r="P152" s="40"/>
@@ -21786,30 +21786,30 @@
         <v>4</v>
       </c>
       <c r="D153" s="19" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="E153" s="19" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="F153" s="19" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="G153" s="19"/>
       <c r="H153" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I153" s="20" t="s">
-        <v>592</v>
+        <v>589</v>
       </c>
       <c r="J153" s="20"/>
       <c r="K153" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L153" s="20">
         <v>20</v>
       </c>
       <c r="M153" s="19" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="N153" s="19"/>
       <c r="O153" s="18"/>
@@ -21906,7 +21906,7 @@
         <v>222</v>
       </c>
       <c r="E154" s="19" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F154" s="19" t="s">
         <v>227</v>
@@ -21924,13 +21924,13 @@
         <v>99</v>
       </c>
       <c r="K154" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L154" s="20">
         <v>30</v>
       </c>
       <c r="M154" s="19" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="N154" s="19"/>
       <c r="O154" s="18"/>
@@ -22024,13 +22024,13 @@
         <v>5</v>
       </c>
       <c r="D155" s="34" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="E155" s="34" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="F155" s="34" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="G155" s="34" t="s">
         <v>84</v>
@@ -22039,20 +22039,20 @@
         <v>193</v>
       </c>
       <c r="I155" s="33" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="J155" s="33"/>
       <c r="K155" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L155" s="33">
         <v>40</v>
       </c>
       <c r="M155" s="34" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="N155" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O155" s="35">
         <v>1</v>
@@ -22147,22 +22147,22 @@
         <v>5</v>
       </c>
       <c r="D156" s="34" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="E156" s="34" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F156" s="34" t="s">
-        <v>743</v>
+        <v>739</v>
       </c>
       <c r="G156" s="34" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="H156" s="34" t="s">
         <v>193</v>
       </c>
       <c r="I156" s="33" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="J156" s="33">
         <v>2</v>
@@ -22174,10 +22174,10 @@
         <v>309</v>
       </c>
       <c r="M156" s="34" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="N156" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O156" s="35">
         <v>1</v>
@@ -22272,13 +22272,13 @@
         <v>5</v>
       </c>
       <c r="D157" s="19" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E157" s="19" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F157" s="19" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="G157" s="19" t="s">
         <v>84</v>
@@ -22287,13 +22287,13 @@
         <v>193</v>
       </c>
       <c r="I157" s="20" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="J157" s="20">
         <v>1</v>
       </c>
       <c r="K157" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L157" s="20" t="s">
         <v>309</v>
@@ -22393,13 +22393,13 @@
         <v>5</v>
       </c>
       <c r="D158" s="37" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="E158" s="37" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F158" s="37" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G158" s="37" t="s">
         <v>131</v>
@@ -22408,22 +22408,22 @@
         <v>193</v>
       </c>
       <c r="I158" s="36" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="J158" s="36">
         <v>99</v>
       </c>
       <c r="K158" s="36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L158" s="36">
         <v>40</v>
       </c>
       <c r="M158" s="37" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="N158" s="37" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="O158" s="38"/>
       <c r="P158" s="36"/>
@@ -22516,33 +22516,33 @@
         <v>5</v>
       </c>
       <c r="D159" s="34" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="E159" s="34" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="F159" s="34" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="G159" s="34"/>
       <c r="H159" s="34" t="s">
         <v>193</v>
       </c>
       <c r="I159" s="33" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="J159" s="33"/>
       <c r="K159" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L159" s="33">
         <v>35</v>
       </c>
       <c r="M159" s="34" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="N159" s="34" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="O159" s="35">
         <v>1</v>
@@ -22637,13 +22637,13 @@
         <v>5</v>
       </c>
       <c r="D160" s="34" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="E160" s="34" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F160" s="34" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="G160" s="34" t="s">
         <v>90</v>
@@ -22652,7 +22652,7 @@
         <v>193</v>
       </c>
       <c r="I160" s="33" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J160" s="33">
         <v>2</v>
@@ -22664,10 +22664,10 @@
         <v>309</v>
       </c>
       <c r="M160" s="34" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="N160" s="34" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="O160" s="35">
         <v>1</v>
@@ -22762,33 +22762,33 @@
         <v>5</v>
       </c>
       <c r="D161" s="37" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="E161" s="37" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="F161" s="37" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="G161" s="37"/>
       <c r="H161" s="37" t="s">
         <v>193</v>
       </c>
       <c r="I161" s="36" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="J161" s="36"/>
       <c r="K161" s="36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L161" s="36">
         <v>35</v>
       </c>
       <c r="M161" s="37" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="N161" s="37" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O161" s="38"/>
       <c r="P161" s="36"/>
@@ -23020,7 +23020,7 @@
         <v>1</v>
       </c>
       <c r="K163" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L163" s="20" t="s">
         <v>309</v>
@@ -23141,7 +23141,7 @@
         <v>7</v>
       </c>
       <c r="K164" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L164" s="20" t="s">
         <v>314</v>
@@ -23241,13 +23241,13 @@
         <v>6</v>
       </c>
       <c r="D165" s="34" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="E165" s="34" t="s">
         <v>50</v>
       </c>
       <c r="F165" s="34" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G165" s="34" t="s">
         <v>72</v>
@@ -23256,7 +23256,7 @@
         <v>193</v>
       </c>
       <c r="I165" s="33" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="J165" s="33">
         <v>4</v>
@@ -23268,10 +23268,10 @@
         <v>309</v>
       </c>
       <c r="M165" s="34" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="N165" s="34" t="s">
-        <v>875</v>
+        <v>870</v>
       </c>
       <c r="O165" s="35">
         <v>1</v>
@@ -23366,13 +23366,13 @@
         <v>6</v>
       </c>
       <c r="D166" s="19" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E166" s="19" t="s">
         <v>50</v>
       </c>
       <c r="F166" s="19" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="G166" s="19" t="s">
         <v>109</v>
@@ -23381,13 +23381,13 @@
         <v>193</v>
       </c>
       <c r="I166" s="20" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="J166" s="20">
         <v>99</v>
       </c>
       <c r="K166" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L166" s="20" t="s">
         <v>314</v>
@@ -23502,7 +23502,7 @@
         <v>193</v>
       </c>
       <c r="I167" s="30" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="J167" s="30">
         <v>2</v>
@@ -23616,7 +23616,7 @@
         <v>89</v>
       </c>
       <c r="F168" s="19" t="s">
-        <v>363</v>
+        <v>907</v>
       </c>
       <c r="G168" s="19" t="s">
         <v>102</v>
@@ -23631,7 +23631,7 @@
         <v>5</v>
       </c>
       <c r="K168" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L168" s="20">
         <v>20</v>
@@ -23761,7 +23761,7 @@
         <v>199</v>
       </c>
       <c r="N169" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O169" s="35">
         <v>1</v>
@@ -23864,7 +23864,7 @@
         <v>38</v>
       </c>
       <c r="F170" s="34" t="s">
-        <v>665</v>
+        <v>909</v>
       </c>
       <c r="G170" s="34" t="s">
         <v>84</v>
@@ -23888,7 +23888,7 @@
         <v>199</v>
       </c>
       <c r="N170" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O170" s="35">
         <v>1</v>
@@ -24015,7 +24015,7 @@
         <v>199</v>
       </c>
       <c r="N171" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O171" s="35">
         <v>1</v>
@@ -24118,16 +24118,16 @@
         <v>38</v>
       </c>
       <c r="F172" s="34" t="s">
-        <v>774</v>
+        <v>910</v>
       </c>
       <c r="G172" s="34" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="H172" s="34" t="s">
         <v>193</v>
       </c>
       <c r="I172" s="33" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="J172" s="33">
         <v>1</v>
@@ -24142,7 +24142,7 @@
         <v>199</v>
       </c>
       <c r="N172" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O172" s="35">
         <v>1</v>
@@ -24245,7 +24245,7 @@
         <v>38</v>
       </c>
       <c r="F173" s="34" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G173" s="34" t="s">
         <v>90</v>
@@ -24254,7 +24254,7 @@
         <v>193</v>
       </c>
       <c r="I173" s="33" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J173" s="33">
         <v>2</v>
@@ -24269,7 +24269,7 @@
         <v>199</v>
       </c>
       <c r="N173" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O173" s="35">
         <v>1</v>
@@ -24366,13 +24366,13 @@
         <v>7</v>
       </c>
       <c r="D174" s="37" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E174" s="37" t="s">
         <v>38</v>
       </c>
       <c r="F174" s="37" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="G174" s="37" t="s">
         <v>112</v>
@@ -24381,7 +24381,7 @@
         <v>193</v>
       </c>
       <c r="I174" s="36" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="J174" s="36">
         <v>3</v>
@@ -24396,7 +24396,7 @@
         <v>199</v>
       </c>
       <c r="N174" s="37" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="O174" s="38"/>
       <c r="P174" s="36"/>
@@ -24489,13 +24489,13 @@
         <v>7</v>
       </c>
       <c r="D175" s="37" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="E175" s="37" t="s">
         <v>38</v>
       </c>
       <c r="F175" s="37" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="G175" s="37" t="s">
         <v>147</v>
@@ -24504,7 +24504,7 @@
         <v>193</v>
       </c>
       <c r="I175" s="36" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="J175" s="36">
         <v>99</v>
@@ -24519,7 +24519,7 @@
         <v>199</v>
       </c>
       <c r="N175" s="37" t="s">
-        <v>868</v>
+        <v>863</v>
       </c>
       <c r="O175" s="38"/>
       <c r="P175" s="36"/>
@@ -24612,13 +24612,13 @@
         <v>7</v>
       </c>
       <c r="D176" s="19" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="E176" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F176" s="19" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="G176" s="19" t="s">
         <v>170</v>
@@ -24627,13 +24627,13 @@
         <v>193</v>
       </c>
       <c r="I176" s="20" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="J176" s="20">
         <v>99</v>
       </c>
       <c r="K176" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L176" s="20" t="s">
         <v>298</v>
@@ -24739,7 +24739,7 @@
         <v>38</v>
       </c>
       <c r="F177" s="19" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G177" s="19" t="s">
         <v>191</v>
@@ -24748,13 +24748,13 @@
         <v>193</v>
       </c>
       <c r="I177" s="20" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J177" s="20">
         <v>3</v>
       </c>
       <c r="K177" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L177" s="20" t="s">
         <v>298</v>
@@ -24860,22 +24860,22 @@
         <v>38</v>
       </c>
       <c r="F178" s="19" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="G178" s="19" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="H178" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I178" s="20" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J178" s="20">
         <v>99</v>
       </c>
       <c r="K178" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L178" s="20" t="s">
         <v>298</v>
@@ -25102,7 +25102,7 @@
         <v>38</v>
       </c>
       <c r="F180" s="19" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="G180" s="19" t="s">
         <v>147</v>
@@ -25111,13 +25111,13 @@
         <v>193</v>
       </c>
       <c r="I180" s="20" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J180" s="20">
         <v>99</v>
       </c>
       <c r="K180" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L180" s="20" t="s">
         <v>298</v>
@@ -25344,7 +25344,7 @@
         <v>38</v>
       </c>
       <c r="F182" s="19" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="G182" s="19" t="s">
         <v>103</v>
@@ -25465,7 +25465,7 @@
         <v>38</v>
       </c>
       <c r="F183" s="34" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="G183" s="34" t="s">
         <v>146</v>
@@ -25480,7 +25480,7 @@
         <v>99</v>
       </c>
       <c r="K183" s="33" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L183" s="33" t="s">
         <v>298</v>
@@ -25489,7 +25489,7 @@
         <v>199</v>
       </c>
       <c r="N183" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O183" s="35">
         <v>1</v>
@@ -25607,7 +25607,7 @@
         <v>99</v>
       </c>
       <c r="K184" s="36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L184" s="36">
         <v>4</v>
@@ -25616,7 +25616,7 @@
         <v>199</v>
       </c>
       <c r="N184" s="37" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O184" s="38"/>
       <c r="P184" s="36"/>
@@ -25833,7 +25833,7 @@
         <v>38</v>
       </c>
       <c r="F186" s="19" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="G186" s="19" t="s">
         <v>188</v>
@@ -25848,7 +25848,7 @@
         <v>99</v>
       </c>
       <c r="K186" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L186" s="20" t="s">
         <v>298</v>
@@ -26077,7 +26077,7 @@
         <v>38</v>
       </c>
       <c r="F188" s="19" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="G188" s="19" t="s">
         <v>110</v>
@@ -26092,7 +26092,7 @@
         <v>1</v>
       </c>
       <c r="K188" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L188" s="20" t="s">
         <v>298</v>
@@ -26192,13 +26192,13 @@
         <v>7</v>
       </c>
       <c r="D189" s="19" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E189" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F189" s="19" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="G189" s="19" t="s">
         <v>84</v>
@@ -26207,7 +26207,7 @@
         <v>193</v>
       </c>
       <c r="I189" s="20" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="J189" s="20">
         <v>1</v>
@@ -26319,16 +26319,16 @@
         <v>99</v>
       </c>
       <c r="F190" s="19" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="G190" s="19" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="H190" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I190" s="20" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="J190" s="20">
         <v>99</v>
@@ -26561,7 +26561,7 @@
         <v>99</v>
       </c>
       <c r="F192" s="19" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G192" s="19" t="s">
         <v>90</v>
@@ -26682,7 +26682,7 @@
         <v>38</v>
       </c>
       <c r="F193" s="34" t="s">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G193" s="34" t="s">
         <v>72</v>
@@ -26706,7 +26706,7 @@
         <v>199</v>
       </c>
       <c r="N193" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O193" s="35">
         <v>1</v>
@@ -26818,7 +26818,7 @@
         <v>193</v>
       </c>
       <c r="I194" s="33" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="J194" s="33">
         <v>6</v>
@@ -26833,7 +26833,7 @@
         <v>199</v>
       </c>
       <c r="N194" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O194" s="35">
         <v>1</v>
@@ -26960,7 +26960,7 @@
         <v>199</v>
       </c>
       <c r="N195" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O195" s="35">
         <v>1</v>
@@ -27063,7 +27063,7 @@
         <v>55</v>
       </c>
       <c r="F196" s="19" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="G196" s="19" t="s">
         <v>112</v>
@@ -27084,7 +27084,7 @@
         <v>317</v>
       </c>
       <c r="M196" s="19" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="N196" s="19"/>
       <c r="O196" s="18"/>
@@ -27199,7 +27199,7 @@
         <v>99</v>
       </c>
       <c r="K197" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L197" s="20" t="s">
         <v>298</v>
@@ -27320,7 +27320,7 @@
         <v>7</v>
       </c>
       <c r="K198" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L198" s="20" t="s">
         <v>298</v>
@@ -27441,7 +27441,7 @@
         <v>99</v>
       </c>
       <c r="K199" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L199" s="20" t="s">
         <v>298</v>
@@ -27541,13 +27541,13 @@
         <v>7</v>
       </c>
       <c r="D200" s="19" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E200" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F200" s="19" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="G200" s="19" t="s">
         <v>72</v>
@@ -27556,7 +27556,7 @@
         <v>193</v>
       </c>
       <c r="I200" s="20" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="J200" s="20">
         <v>4</v>
@@ -27662,13 +27662,13 @@
         <v>7</v>
       </c>
       <c r="D201" s="19" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="E201" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F201" s="19" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="G201" s="19" t="s">
         <v>102</v>
@@ -27677,7 +27677,7 @@
         <v>193</v>
       </c>
       <c r="I201" s="20" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="J201" s="20">
         <v>99</v>
@@ -27789,7 +27789,7 @@
         <v>38</v>
       </c>
       <c r="F202" s="34" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="G202" s="34" t="s">
         <v>84</v>
@@ -27813,7 +27813,7 @@
         <v>199</v>
       </c>
       <c r="N202" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O202" s="35">
         <v>1</v>
@@ -27938,7 +27938,7 @@
         <v>199</v>
       </c>
       <c r="N203" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O203" s="35">
         <v>1</v>
@@ -28048,7 +28048,7 @@
         <v>193</v>
       </c>
       <c r="I204" s="20" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="J204" s="20">
         <v>6</v>
@@ -28160,16 +28160,16 @@
         <v>38</v>
       </c>
       <c r="F205" s="19" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G205" s="19" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="H205" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I205" s="20" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="J205" s="20">
         <v>99</v>
@@ -28275,13 +28275,13 @@
         <v>7</v>
       </c>
       <c r="D206" s="34" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="E206" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F206" s="34" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="G206" s="34" t="s">
         <v>72</v>
@@ -28290,7 +28290,7 @@
         <v>193</v>
       </c>
       <c r="I206" s="33" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="J206" s="33">
         <v>4</v>
@@ -28305,7 +28305,7 @@
         <v>199</v>
       </c>
       <c r="N206" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O206" s="35">
         <v>1</v>
@@ -28400,13 +28400,13 @@
         <v>7</v>
       </c>
       <c r="D207" s="34" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="E207" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F207" s="34" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="G207" s="34" t="s">
         <v>90</v>
@@ -28415,7 +28415,7 @@
         <v>193</v>
       </c>
       <c r="I207" s="33" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="J207" s="33">
         <v>2</v>
@@ -28430,7 +28430,7 @@
         <v>199</v>
       </c>
       <c r="N207" s="34" t="s">
-        <v>876</v>
+        <v>871</v>
       </c>
       <c r="O207" s="35">
         <v>1</v>
@@ -28531,7 +28531,7 @@
         <v>38</v>
       </c>
       <c r="F208" s="34" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="G208" s="34" t="s">
         <v>84</v>
@@ -28555,7 +28555,7 @@
         <v>199</v>
       </c>
       <c r="N208" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O208" s="35">
         <v>1</v>
@@ -28655,10 +28655,10 @@
         <v>345</v>
       </c>
       <c r="E209" s="34" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="F209" s="34" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G209" s="34" t="s">
         <v>90</v>
@@ -28667,7 +28667,7 @@
         <v>193</v>
       </c>
       <c r="I209" s="33" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="J209" s="33">
         <v>2</v>
@@ -28682,7 +28682,7 @@
         <v>105</v>
       </c>
       <c r="N209" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O209" s="35">
         <v>1</v>
@@ -28779,28 +28779,28 @@
         <v>7</v>
       </c>
       <c r="D210" s="19" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E210" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F210" s="19" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="G210" s="19" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="H210" s="19" t="s">
         <v>193</v>
       </c>
       <c r="I210" s="20" t="s">
-        <v>570</v>
+        <v>567</v>
       </c>
       <c r="J210" s="20">
         <v>1</v>
       </c>
       <c r="K210" s="20" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="L210" s="20" t="s">
         <v>298</v>
@@ -29027,7 +29027,7 @@
         <v>55</v>
       </c>
       <c r="F212" s="31" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G212" s="31" t="s">
         <v>90</v>
@@ -29150,16 +29150,16 @@
         <v>55</v>
       </c>
       <c r="F213" s="31" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="G213" s="31" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="H213" s="31" t="s">
         <v>193</v>
       </c>
       <c r="I213" s="30" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="J213" s="30">
         <v>1</v>
@@ -29273,16 +29273,16 @@
         <v>55</v>
       </c>
       <c r="F214" s="34" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G214" s="34" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="H214" s="34" t="s">
         <v>193</v>
       </c>
       <c r="I214" s="33" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="J214" s="33">
         <v>1</v>
@@ -29297,7 +29297,7 @@
         <v>105</v>
       </c>
       <c r="N214" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O214" s="35">
         <v>1</v>
@@ -29400,7 +29400,7 @@
         <v>55</v>
       </c>
       <c r="F215" s="34" t="s">
-        <v>377</v>
+        <v>908</v>
       </c>
       <c r="G215" s="34" t="s">
         <v>147</v>
@@ -29409,7 +29409,7 @@
         <v>193</v>
       </c>
       <c r="I215" s="33" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="J215" s="33">
         <v>99</v>
@@ -29424,7 +29424,7 @@
         <v>105</v>
       </c>
       <c r="N215" s="34" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="O215" s="35">
         <v>1</v>
@@ -29548,7 +29548,7 @@
         <v>316</v>
       </c>
       <c r="N216" s="37" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="O216" s="38"/>
       <c r="P216" s="36"/>

--- a/Torino_2027.xlsx
+++ b/Torino_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24B83BA-4431-405D-8304-F26C82C015F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB27B1CA-F50C-4B36-983E-39A043C48DFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{65E54767-2A5A-433C-9949-276C98563996}"/>
   </bookViews>
@@ -619,9 +619,6 @@
     <t>011/8600242</t>
   </si>
   <si>
-    <t>Via Bologna, 20</t>
-  </si>
-  <si>
     <t>011/0897651</t>
   </si>
   <si>
@@ -979,9 +976,6 @@
     <t>Via Belfiore, 48</t>
   </si>
   <si>
-    <t>Via Cibrario, 3/bis</t>
-  </si>
-  <si>
     <t>Via Monte di Pietà, 17/C</t>
   </si>
   <si>
@@ -2812,9 +2806,6 @@
     <t>011/5175087</t>
   </si>
   <si>
-    <t>Via dei Mercanti, 8b</t>
-  </si>
-  <si>
     <t>bloccato per Andrea Bernardi</t>
   </si>
   <si>
@@ -2852,6 +2843,15 @@
   </si>
   <si>
     <t>Via Principi d'Acaja, 65/D</t>
+  </si>
+  <si>
+    <t>Via dei Mercanti, 8</t>
+  </si>
+  <si>
+    <t>Via Luigi Cibrario, 9</t>
+  </si>
+  <si>
+    <t>Via Bologna, 20/a</t>
   </si>
 </sst>
 </file>
@@ -3693,7 +3693,7 @@
         <v>18</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="4" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -3747,7 +3747,7 @@
         <v>120</v>
       </c>
       <c r="I5" s="22" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="13"/>
@@ -3858,13 +3858,13 @@
     </row>
     <row r="7" spans="1:45" s="26" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="23" t="s">
+        <v>690</v>
+      </c>
+      <c r="B7" s="23" t="s">
+        <v>691</v>
+      </c>
+      <c r="C7" s="23" t="s">
         <v>692</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>693</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>694</v>
       </c>
       <c r="D7" s="27" t="s">
         <v>13</v>
@@ -3879,22 +3879,22 @@
         <v>20</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I7" s="23" t="s">
         <v>11</v>
       </c>
       <c r="J7" s="23" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="K7" s="29" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="L7" s="23" t="s">
         <v>19</v>
       </c>
       <c r="M7" s="27" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="N7" s="24" t="s">
         <v>0</v>
@@ -3987,37 +3987,37 @@
         <v>1</v>
       </c>
       <c r="D8" s="34" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G8" s="34" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="H8" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="J8" s="33">
         <v>99</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L8" s="33" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="M8" s="34" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="N8" s="34" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="O8" s="35">
         <v>1</v>
@@ -4112,28 +4112,28 @@
         <v>1</v>
       </c>
       <c r="D9" s="31" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="F9" s="31" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G9" s="31" t="s">
         <v>90</v>
       </c>
       <c r="H9" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I9" s="30" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="J9" s="30">
         <v>2</v>
       </c>
       <c r="K9" s="30" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L9" s="30" t="s">
         <v>105</v>
@@ -4235,10 +4235,10 @@
         <v>1</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F10" s="34" t="s">
         <v>153</v>
@@ -4247,7 +4247,7 @@
         <v>103</v>
       </c>
       <c r="H10" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I10" s="33" t="s">
         <v>154</v>
@@ -4256,16 +4256,16 @@
         <v>7</v>
       </c>
       <c r="K10" s="33" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="L10" s="33">
         <v>130</v>
       </c>
       <c r="M10" s="34" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="N10" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O10" s="35">
         <v>1</v>
@@ -4363,34 +4363,34 @@
         <v>164</v>
       </c>
       <c r="E11" s="37" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>166</v>
+        <v>910</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>109</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I11" s="36" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="J11" s="36">
         <v>99</v>
       </c>
       <c r="K11" s="36" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="L11" s="36" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="M11" s="37" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="N11" s="37" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="O11" s="38"/>
       <c r="P11" s="36"/>
@@ -4483,34 +4483,34 @@
         <v>1</v>
       </c>
       <c r="D12" s="41" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E12" s="41" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F12" s="41" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G12" s="41" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H12" s="41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I12" s="40" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="J12" s="40">
         <v>99</v>
       </c>
       <c r="K12" s="40" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L12" s="40" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="M12" s="41" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="N12" s="41"/>
       <c r="O12" s="42"/>
@@ -4604,28 +4604,28 @@
         <v>1</v>
       </c>
       <c r="D13" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="G13" s="34" t="s">
+        <v>558</v>
+      </c>
+      <c r="H13" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="I13" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="E13" s="34" t="s">
-        <v>239</v>
-      </c>
-      <c r="F13" s="34" t="s">
-        <v>288</v>
-      </c>
-      <c r="G13" s="34" t="s">
-        <v>560</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="I13" s="33" t="s">
-        <v>257</v>
-      </c>
       <c r="J13" s="33">
         <v>1</v>
       </c>
       <c r="K13" s="33" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="L13" s="33" t="s">
         <v>105</v>
@@ -4634,7 +4634,7 @@
         <v>105</v>
       </c>
       <c r="N13" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O13" s="35">
         <v>1</v>
@@ -4731,37 +4731,37 @@
         <v>1</v>
       </c>
       <c r="D14" s="37" t="s">
+        <v>588</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="F14" s="37" t="s">
         <v>590</v>
-      </c>
-      <c r="E14" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="F14" s="37" t="s">
-        <v>592</v>
       </c>
       <c r="G14" s="37" t="s">
         <v>90</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I14" s="36" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="J14" s="36">
         <v>2</v>
       </c>
       <c r="K14" s="36" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L14" s="36">
         <v>75</v>
       </c>
       <c r="M14" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N14" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="O14" s="38"/>
       <c r="P14" s="36"/>
@@ -4854,24 +4854,24 @@
         <v>2</v>
       </c>
       <c r="D15" s="31" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F15" s="31" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G15" s="31"/>
       <c r="H15" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I15" s="30" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="J15" s="30"/>
       <c r="K15" s="30" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L15" s="30"/>
       <c r="M15" s="31"/>
@@ -4969,34 +4969,34 @@
         <v>2</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G16" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I16" s="20" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="J16" s="20">
         <v>1</v>
       </c>
       <c r="K16" s="20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M16" s="19" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N16" s="19"/>
       <c r="O16" s="18"/>
@@ -5090,37 +5090,37 @@
         <v>2</v>
       </c>
       <c r="D17" s="34" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F17" s="34" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G17" s="34" t="s">
         <v>105</v>
       </c>
       <c r="H17" s="34" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="I17" s="33" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="J17" s="33">
         <v>99</v>
       </c>
       <c r="K17" s="33" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L17" s="33">
         <v>47</v>
       </c>
       <c r="M17" s="34" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="N17" s="34" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="O17" s="35">
         <v>1</v>
@@ -5215,35 +5215,35 @@
         <v>2</v>
       </c>
       <c r="D18" s="37" t="s">
+        <v>823</v>
+      </c>
+      <c r="E18" s="37" t="s">
+        <v>237</v>
+      </c>
+      <c r="F18" s="37" t="s">
         <v>825</v>
       </c>
-      <c r="E18" s="37" t="s">
-        <v>238</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>827</v>
-      </c>
       <c r="G18" s="37" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="H18" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="J18" s="36"/>
       <c r="K18" s="36" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L18" s="36">
         <v>45</v>
       </c>
       <c r="M18" s="37" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="N18" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O18" s="38"/>
       <c r="P18" s="36"/>
@@ -5336,34 +5336,34 @@
         <v>2</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G19" s="19" t="s">
         <v>85</v>
       </c>
       <c r="H19" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I19" s="20" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="J19" s="20">
         <v>6</v>
       </c>
       <c r="K19" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L19" s="20" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M19" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N19" s="19"/>
       <c r="O19" s="18"/>
@@ -5460,16 +5460,16 @@
         <v>59</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="G20" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H20" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I20" s="20" t="s">
         <v>60</v>
@@ -5478,13 +5478,13 @@
         <v>1</v>
       </c>
       <c r="K20" s="20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L20" s="20" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M20" s="19" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="N20" s="19"/>
       <c r="O20" s="18"/>
@@ -5578,34 +5578,34 @@
         <v>2</v>
       </c>
       <c r="D21" s="19" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="G21" s="19" t="s">
         <v>72</v>
       </c>
       <c r="H21" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I21" s="20" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="J21" s="20">
         <v>4</v>
       </c>
       <c r="K21" s="20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L21" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M21" s="19" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="N21" s="19"/>
       <c r="O21" s="18"/>
@@ -5699,19 +5699,19 @@
         <v>2</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G22" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H22" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I22" s="20" t="s">
         <v>165</v>
@@ -5720,13 +5720,13 @@
         <v>1</v>
       </c>
       <c r="K22" s="20" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L22" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M22" s="19" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="N22" s="19"/>
       <c r="O22" s="18"/>
@@ -5823,7 +5823,7 @@
         <v>150</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F23" s="19" t="s">
         <v>151</v>
@@ -5832,7 +5832,7 @@
         <v>109</v>
       </c>
       <c r="H23" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I23" s="20" t="s">
         <v>152</v>
@@ -5841,13 +5841,13 @@
         <v>99</v>
       </c>
       <c r="K23" s="20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L23" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M23" s="19" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N23" s="19"/>
       <c r="O23" s="18"/>
@@ -5941,37 +5941,37 @@
         <v>2</v>
       </c>
       <c r="D24" s="37" t="s">
+        <v>279</v>
+      </c>
+      <c r="E24" s="37" t="s">
         <v>280</v>
       </c>
-      <c r="E24" s="37" t="s">
-        <v>281</v>
-      </c>
       <c r="F24" s="37" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="G24" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="J24" s="36">
         <v>1</v>
       </c>
       <c r="K24" s="36" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L24" s="36" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="M24" s="37" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="N24" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O24" s="38"/>
       <c r="P24" s="36"/>
@@ -6064,37 +6064,37 @@
         <v>2</v>
       </c>
       <c r="D25" s="37" t="s">
+        <v>606</v>
+      </c>
+      <c r="E25" s="37" t="s">
+        <v>280</v>
+      </c>
+      <c r="F25" s="37" t="s">
+        <v>607</v>
+      </c>
+      <c r="G25" s="37" t="s">
         <v>608</v>
       </c>
-      <c r="E25" s="37" t="s">
-        <v>281</v>
-      </c>
-      <c r="F25" s="37" t="s">
+      <c r="H25" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="I25" s="36" t="s">
         <v>609</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>610</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="I25" s="36" t="s">
-        <v>611</v>
       </c>
       <c r="J25" s="36">
         <v>99</v>
       </c>
       <c r="K25" s="36" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L25" s="36" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="M25" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N25" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="O25" s="38"/>
       <c r="P25" s="36"/>
@@ -6187,37 +6187,37 @@
         <v>2</v>
       </c>
       <c r="D26" s="37" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E26" s="37" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F26" s="37" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G26" s="37" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I26" s="36" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="J26" s="36">
         <v>7</v>
       </c>
       <c r="K26" s="36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L26" s="36" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="M26" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N26" s="37" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="O26" s="38"/>
       <c r="P26" s="36"/>
@@ -6310,7 +6310,7 @@
         <v>75</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F27" s="31" t="s">
         <v>115</v>
@@ -6319,7 +6319,7 @@
         <v>84</v>
       </c>
       <c r="H27" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I27" s="30" t="s">
         <v>76</v>
@@ -6328,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="K27" s="30" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L27" s="30" t="s">
         <v>105</v>
@@ -6430,34 +6430,34 @@
         <v>2</v>
       </c>
       <c r="D28" s="19" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="F28" s="19" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G28" s="19" t="s">
         <v>139</v>
       </c>
       <c r="H28" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I28" s="20" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="J28" s="20">
         <v>6</v>
       </c>
       <c r="K28" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L28" s="20" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="M28" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N28" s="19"/>
       <c r="O28" s="18"/>
@@ -6551,37 +6551,37 @@
         <v>2</v>
       </c>
       <c r="D29" s="34" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F29" s="34" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G29" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H29" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I29" s="33" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="J29" s="33">
         <v>2</v>
       </c>
       <c r="K29" s="33" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L29" s="33" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M29" s="34" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="N29" s="34" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="O29" s="35">
         <v>1</v>
@@ -6676,35 +6676,35 @@
         <v>2</v>
       </c>
       <c r="D30" s="37" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E30" s="37" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G30" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H30" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I30" s="36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="J30" s="36">
         <v>1</v>
       </c>
       <c r="K30" s="36" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L30" s="36"/>
       <c r="M30" s="37" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="N30" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="O30" s="38"/>
       <c r="P30" s="36"/>
@@ -6797,37 +6797,37 @@
         <v>2</v>
       </c>
       <c r="D31" s="37" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="E31" s="37" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="G31" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H31" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="J31" s="36">
         <v>1</v>
       </c>
       <c r="K31" s="36" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L31" s="36" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="M31" s="37" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="N31" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O31" s="38"/>
       <c r="P31" s="36"/>
@@ -6920,37 +6920,37 @@
         <v>2</v>
       </c>
       <c r="D32" s="37" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E32" s="37" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G32" s="37" t="s">
         <v>112</v>
       </c>
       <c r="H32" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I32" s="36" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="J32" s="36">
         <v>3</v>
       </c>
       <c r="K32" s="36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L32" s="36" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M32" s="37" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="N32" s="37" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="O32" s="38"/>
       <c r="P32" s="36"/>
@@ -7043,29 +7043,29 @@
         <v>2</v>
       </c>
       <c r="D33" s="34" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="E33" s="34"/>
       <c r="F33" s="34" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="G33" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H33" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I33" s="33" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="J33" s="33"/>
       <c r="K33" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L33" s="33"/>
       <c r="M33" s="34"/>
       <c r="N33" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O33" s="35">
         <v>1</v>
@@ -7162,32 +7162,32 @@
         <v>2</v>
       </c>
       <c r="D34" s="19" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="G34" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="J34" s="20"/>
       <c r="K34" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L34" s="20">
         <v>75</v>
       </c>
       <c r="M34" s="19" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="N34" s="19"/>
       <c r="O34" s="18"/>
@@ -7281,34 +7281,34 @@
         <v>2</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="G35" s="19" t="s">
         <v>90</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I35" s="20" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="J35" s="20">
         <v>2</v>
       </c>
       <c r="K35" s="20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L35" s="20" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M35" s="19" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="N35" s="19"/>
       <c r="O35" s="18"/>
@@ -7402,37 +7402,37 @@
         <v>3</v>
       </c>
       <c r="D36" s="37" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E36" s="37" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G36" s="37" t="s">
         <v>103</v>
       </c>
       <c r="H36" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I36" s="36" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J36" s="36">
         <v>7</v>
       </c>
       <c r="K36" s="36" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L36" s="36" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M36" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N36" s="37" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="O36" s="38"/>
       <c r="P36" s="36"/>
@@ -7528,7 +7528,7 @@
         <v>80</v>
       </c>
       <c r="E37" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F37" s="34" t="s">
         <v>28</v>
@@ -7537,7 +7537,7 @@
         <v>90</v>
       </c>
       <c r="H37" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I37" s="33" t="s">
         <v>29</v>
@@ -7546,16 +7546,16 @@
         <v>2</v>
       </c>
       <c r="K37" s="33" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L37" s="33" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="M37" s="34" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="N37" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O37" s="35">
         <v>1</v>
@@ -7652,37 +7652,37 @@
         <v>3</v>
       </c>
       <c r="D38" s="37" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="E38" s="37" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F38" s="37" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G38" s="37" t="s">
         <v>105</v>
       </c>
       <c r="H38" s="37" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="I38" s="36" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="J38" s="36">
         <v>99</v>
       </c>
       <c r="K38" s="36" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L38" s="36">
         <v>65</v>
       </c>
       <c r="M38" s="37" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="N38" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="O38" s="38"/>
       <c r="P38" s="36"/>
@@ -7775,34 +7775,34 @@
         <v>3</v>
       </c>
       <c r="D39" s="19" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F39" s="19" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="G39" s="19" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H39" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I39" s="20" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="J39" s="20">
         <v>99</v>
       </c>
       <c r="K39" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L39" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M39" s="19" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="N39" s="19"/>
       <c r="O39" s="18"/>
@@ -7896,37 +7896,37 @@
         <v>3</v>
       </c>
       <c r="D40" s="37" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F40" s="37" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="G40" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H40" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I40" s="36" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="J40" s="36">
         <v>1</v>
       </c>
       <c r="K40" s="36" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L40" s="36">
         <v>50</v>
       </c>
       <c r="M40" s="37" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="N40" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="O40" s="38"/>
       <c r="P40" s="36"/>
@@ -8019,37 +8019,37 @@
         <v>3</v>
       </c>
       <c r="D41" s="34" t="s">
+        <v>700</v>
+      </c>
+      <c r="E41" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="F41" s="34" t="s">
         <v>702</v>
-      </c>
-      <c r="E41" s="34" t="s">
-        <v>237</v>
-      </c>
-      <c r="F41" s="34" t="s">
-        <v>704</v>
       </c>
       <c r="G41" s="34" t="s">
         <v>104</v>
       </c>
       <c r="H41" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I41" s="33" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="J41" s="33">
         <v>2</v>
       </c>
       <c r="K41" s="33" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L41" s="33" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M41" s="34" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="N41" s="34" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="O41" s="35">
         <v>1</v>
@@ -8147,7 +8147,7 @@
         <v>148</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F42" s="19" t="s">
         <v>149</v>
@@ -8156,22 +8156,22 @@
         <v>72</v>
       </c>
       <c r="H42" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="I42" s="20" t="s">
         <v>193</v>
-      </c>
-      <c r="I42" s="20" t="s">
-        <v>194</v>
       </c>
       <c r="J42" s="20">
         <v>4</v>
       </c>
       <c r="K42" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L42" s="20">
         <v>40</v>
       </c>
       <c r="M42" s="19" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="N42" s="19"/>
       <c r="O42" s="18"/>
@@ -8265,10 +8265,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F43" s="19" t="s">
         <v>39</v>
@@ -8277,7 +8277,7 @@
         <v>109</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I43" s="20" t="s">
         <v>41</v>
@@ -8286,13 +8286,13 @@
         <v>99</v>
       </c>
       <c r="K43" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L43" s="20">
         <v>30</v>
       </c>
       <c r="M43" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N43" s="19"/>
       <c r="O43" s="18"/>
@@ -8386,34 +8386,34 @@
         <v>3</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="G44" s="19" t="s">
         <v>72</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I44" s="20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J44" s="20">
         <v>4</v>
       </c>
       <c r="K44" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L44" s="20">
         <v>38</v>
       </c>
       <c r="M44" s="19" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="N44" s="19"/>
       <c r="O44" s="18"/>
@@ -8507,34 +8507,34 @@
         <v>3</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G45" s="19" t="s">
         <v>109</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I45" s="20" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="J45" s="20">
         <v>99</v>
       </c>
       <c r="K45" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L45" s="20">
         <v>25</v>
       </c>
       <c r="M45" s="19" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="N45" s="19"/>
       <c r="O45" s="18"/>
@@ -8628,34 +8628,34 @@
         <v>3</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G46" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I46" s="20" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="J46" s="20">
         <v>1</v>
       </c>
       <c r="K46" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L46" s="20">
         <v>35</v>
       </c>
       <c r="M46" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N46" s="19"/>
       <c r="O46" s="18"/>
@@ -8752,34 +8752,34 @@
         <v>57</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F47" s="34" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="G47" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H47" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I47" s="33" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="J47" s="33">
         <v>2</v>
       </c>
       <c r="K47" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L47" s="33" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M47" s="34" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N47" s="34" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="O47" s="35">
         <v>1</v>
@@ -8877,34 +8877,34 @@
         <v>125</v>
       </c>
       <c r="E48" s="37" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="G48" s="37" t="s">
         <v>90</v>
       </c>
       <c r="H48" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I48" s="36" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J48" s="36">
         <v>2</v>
       </c>
       <c r="K48" s="36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L48" s="36" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M48" s="37" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="N48" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O48" s="38"/>
       <c r="P48" s="36"/>
@@ -9000,7 +9000,7 @@
         <v>93</v>
       </c>
       <c r="E49" s="37" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F49" s="37" t="s">
         <v>58</v>
@@ -9009,7 +9009,7 @@
         <v>84</v>
       </c>
       <c r="H49" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I49" s="36" t="s">
         <v>79</v>
@@ -9018,16 +9018,16 @@
         <v>1</v>
       </c>
       <c r="K49" s="36" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L49" s="36" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M49" s="37" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="N49" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O49" s="38"/>
       <c r="P49" s="36"/>
@@ -9120,37 +9120,37 @@
         <v>3</v>
       </c>
       <c r="D50" s="34" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E50" s="34" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F50" s="34" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="G50" s="34" t="s">
         <v>72</v>
       </c>
       <c r="H50" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I50" s="33" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J50" s="33">
         <v>4</v>
       </c>
       <c r="K50" s="33" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L50" s="33">
         <v>45</v>
       </c>
       <c r="M50" s="34" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N50" s="34" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="O50" s="35">
         <v>1</v>
@@ -9245,37 +9245,37 @@
         <v>3</v>
       </c>
       <c r="D51" s="37" t="s">
+        <v>610</v>
+      </c>
+      <c r="E51" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="F51" s="37" t="s">
+        <v>611</v>
+      </c>
+      <c r="G51" s="37" t="s">
+        <v>613</v>
+      </c>
+      <c r="H51" s="37" t="s">
+        <v>192</v>
+      </c>
+      <c r="I51" s="36" t="s">
         <v>612</v>
-      </c>
-      <c r="E51" s="37" t="s">
-        <v>237</v>
-      </c>
-      <c r="F51" s="37" t="s">
-        <v>613</v>
-      </c>
-      <c r="G51" s="37" t="s">
-        <v>615</v>
-      </c>
-      <c r="H51" s="37" t="s">
-        <v>193</v>
-      </c>
-      <c r="I51" s="36" t="s">
-        <v>614</v>
       </c>
       <c r="J51" s="36">
         <v>99</v>
       </c>
       <c r="K51" s="36" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L51" s="36" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="M51" s="37" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="N51" s="37" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="O51" s="38"/>
       <c r="P51" s="36"/>
@@ -9365,34 +9365,34 @@
         <v>3</v>
       </c>
       <c r="D52" s="19" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F52" s="19" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G52" s="19" t="s">
         <v>104</v>
       </c>
       <c r="H52" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I52" s="20" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="J52" s="20">
         <v>2</v>
       </c>
       <c r="K52" s="20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L52" s="20" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M52" s="19" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N52" s="19"/>
       <c r="O52" s="18"/>
@@ -9489,16 +9489,16 @@
         <v>31</v>
       </c>
       <c r="E53" s="37" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F53" s="37" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="G53" s="37" t="s">
         <v>72</v>
       </c>
       <c r="H53" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I53" s="36" t="s">
         <v>32</v>
@@ -9507,16 +9507,16 @@
         <v>4</v>
       </c>
       <c r="K53" s="36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L53" s="36" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M53" s="37" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="N53" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="O53" s="38"/>
       <c r="P53" s="36"/>
@@ -9609,37 +9609,37 @@
         <v>3</v>
       </c>
       <c r="D54" s="37" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E54" s="37" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F54" s="37" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="G54" s="37" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="H54" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I54" s="36" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="J54" s="36">
         <v>7</v>
       </c>
       <c r="K54" s="36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L54" s="36" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M54" s="37" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="N54" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="O54" s="38"/>
       <c r="P54" s="36"/>
@@ -9732,34 +9732,34 @@
         <v>3</v>
       </c>
       <c r="D55" s="41" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E55" s="41" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F55" s="41" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="G55" s="41" t="s">
         <v>105</v>
       </c>
       <c r="H55" s="41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I55" s="40" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="J55" s="40">
         <v>99</v>
       </c>
       <c r="K55" s="40" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L55" s="40" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="M55" s="41" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="N55" s="41"/>
       <c r="O55" s="42"/>
@@ -9853,35 +9853,35 @@
         <v>3</v>
       </c>
       <c r="D56" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F56" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="G56" s="34" t="s">
         <v>111</v>
       </c>
       <c r="H56" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I56" s="33" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="J56" s="33"/>
       <c r="K56" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L56" s="33">
         <v>38</v>
       </c>
       <c r="M56" s="34" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N56" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O56" s="35">
         <v>1</v>
@@ -9978,34 +9978,34 @@
         <v>3</v>
       </c>
       <c r="D57" s="19" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F57" s="19" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="G57" s="19" t="s">
         <v>90</v>
       </c>
       <c r="H57" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I57" s="20" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="J57" s="20">
         <v>2</v>
       </c>
       <c r="K57" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L57" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M57" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N57" s="19"/>
       <c r="O57" s="18"/>
@@ -10099,33 +10099,33 @@
         <v>3</v>
       </c>
       <c r="D58" s="34" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F58" s="34" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G58" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H58" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I58" s="33" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="J58" s="33">
         <v>2</v>
       </c>
       <c r="K58" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L58" s="33"/>
       <c r="M58" s="34"/>
       <c r="N58" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O58" s="35">
         <v>1</v>
@@ -10234,7 +10234,7 @@
         <v>111</v>
       </c>
       <c r="H59" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I59" s="33" t="s">
         <v>124</v>
@@ -10243,16 +10243,16 @@
         <v>99</v>
       </c>
       <c r="K59" s="33" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L59" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M59" s="34" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="N59" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O59" s="35">
         <v>1</v>
@@ -10349,34 +10349,34 @@
         <v>5</v>
       </c>
       <c r="D60" s="19" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F60" s="19" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="G60" s="19" t="s">
         <v>102</v>
       </c>
       <c r="H60" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I60" s="20" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="J60" s="20">
         <v>5</v>
       </c>
       <c r="K60" s="20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L60" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M60" s="19" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="N60" s="19"/>
       <c r="O60" s="18"/>
@@ -10470,33 +10470,33 @@
         <v>5</v>
       </c>
       <c r="D61" s="34" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="E61" s="34" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F61" s="34" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="G61" s="34" t="s">
         <v>72</v>
       </c>
       <c r="H61" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I61" s="33" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="J61" s="33">
         <v>4</v>
       </c>
       <c r="K61" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L61" s="33"/>
       <c r="M61" s="34"/>
       <c r="N61" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O61" s="35">
         <v>1</v>
@@ -10593,34 +10593,34 @@
         <v>5</v>
       </c>
       <c r="D62" s="19" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F62" s="19" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G62" s="19" t="s">
         <v>102</v>
       </c>
       <c r="H62" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I62" s="20" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="J62" s="20">
         <v>5</v>
       </c>
       <c r="K62" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L62" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M62" s="19" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="N62" s="19"/>
       <c r="O62" s="18"/>
@@ -10714,34 +10714,34 @@
         <v>5</v>
       </c>
       <c r="D63" s="19" t="s">
+        <v>740</v>
+      </c>
+      <c r="E63" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="F63" s="19" t="s">
+        <v>741</v>
+      </c>
+      <c r="G63" s="19" t="s">
         <v>742</v>
       </c>
-      <c r="E63" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="F63" s="19" t="s">
+      <c r="H63" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="I63" s="20" t="s">
         <v>743</v>
-      </c>
-      <c r="G63" s="19" t="s">
-        <v>744</v>
-      </c>
-      <c r="H63" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="I63" s="20" t="s">
-        <v>745</v>
       </c>
       <c r="J63" s="20">
         <v>99</v>
       </c>
       <c r="K63" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L63" s="20">
         <v>30</v>
       </c>
       <c r="M63" s="19" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="N63" s="19"/>
       <c r="O63" s="18"/>
@@ -10835,34 +10835,34 @@
         <v>5</v>
       </c>
       <c r="D64" s="19" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F64" s="19" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="G64" s="19" t="s">
         <v>147</v>
       </c>
       <c r="H64" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I64" s="20" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="J64" s="20">
         <v>99</v>
       </c>
       <c r="K64" s="20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L64" s="20">
         <v>40</v>
       </c>
       <c r="M64" s="19" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="N64" s="19"/>
       <c r="O64" s="18"/>
@@ -10956,34 +10956,34 @@
         <v>5</v>
       </c>
       <c r="D65" s="19" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F65" s="19" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="G65" s="19" t="s">
         <v>105</v>
       </c>
       <c r="H65" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I65" s="20" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="J65" s="20">
         <v>99</v>
       </c>
       <c r="K65" s="20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L65" s="20">
         <v>40</v>
       </c>
       <c r="M65" s="19" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="N65" s="19"/>
       <c r="O65" s="18"/>
@@ -11077,37 +11077,37 @@
         <v>5</v>
       </c>
       <c r="D66" s="37" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E66" s="37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G66" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H66" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I66" s="36" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="J66" s="36">
         <v>1</v>
       </c>
       <c r="K66" s="36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L66" s="36" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M66" s="37" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="N66" s="37" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O66" s="38"/>
       <c r="P66" s="36"/>
@@ -11203,7 +11203,7 @@
         <v>126</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F67" s="37" t="s">
         <v>136</v>
@@ -11212,7 +11212,7 @@
         <v>72</v>
       </c>
       <c r="H67" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I67" s="36" t="s">
         <v>127</v>
@@ -11221,16 +11221,16 @@
         <v>4</v>
       </c>
       <c r="K67" s="36" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L67" s="36">
         <v>31</v>
       </c>
       <c r="M67" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="N67" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="O67" s="38"/>
       <c r="P67" s="36"/>
@@ -11323,10 +11323,10 @@
         <v>5</v>
       </c>
       <c r="D68" s="37" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F68" s="37" t="s">
         <v>66</v>
@@ -11335,25 +11335,25 @@
         <v>113</v>
       </c>
       <c r="H68" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I68" s="36" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="J68" s="36">
         <v>5</v>
       </c>
       <c r="K68" s="36" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L68" s="36" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="M68" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N68" s="37" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="O68" s="38"/>
       <c r="P68" s="36"/>
@@ -11446,35 +11446,35 @@
         <v>5</v>
       </c>
       <c r="D69" s="34" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="E69" s="34" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="F69" s="34" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G69" s="34" t="s">
         <v>72</v>
       </c>
       <c r="H69" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I69" s="33" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="J69" s="33"/>
       <c r="K69" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L69" s="33">
         <v>45</v>
       </c>
       <c r="M69" s="34" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="N69" s="34" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="O69" s="35">
         <v>1</v>
@@ -11569,37 +11569,37 @@
         <v>5</v>
       </c>
       <c r="D70" s="37" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E70" s="37" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F70" s="37" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="G70" s="37" t="s">
         <v>139</v>
       </c>
       <c r="H70" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I70" s="36" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="J70" s="36">
         <v>1</v>
       </c>
       <c r="K70" s="36" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L70" s="36" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="M70" s="37" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="N70" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O70" s="38"/>
       <c r="P70" s="36"/>
@@ -11692,37 +11692,37 @@
         <v>5</v>
       </c>
       <c r="D71" s="34" t="s">
+        <v>819</v>
+      </c>
+      <c r="E71" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="F71" s="34" t="s">
+        <v>820</v>
+      </c>
+      <c r="G71" s="34" t="s">
         <v>821</v>
       </c>
-      <c r="E71" s="34" t="s">
-        <v>240</v>
-      </c>
-      <c r="F71" s="34" t="s">
+      <c r="H71" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="I71" s="33" t="s">
         <v>822</v>
       </c>
-      <c r="G71" s="34" t="s">
-        <v>823</v>
-      </c>
-      <c r="H71" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="I71" s="33" t="s">
-        <v>824</v>
-      </c>
       <c r="J71" s="33">
         <v>1</v>
       </c>
       <c r="K71" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L71" s="33">
         <v>35</v>
       </c>
       <c r="M71" s="34" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N71" s="34" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="O71" s="35">
         <v>1</v>
@@ -11817,10 +11817,10 @@
         <v>5</v>
       </c>
       <c r="D72" s="34" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="E72" s="34" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="F72" s="34" t="s">
         <v>68</v>
@@ -11829,25 +11829,25 @@
         <v>90</v>
       </c>
       <c r="H72" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I72" s="33" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="J72" s="33">
         <v>2</v>
       </c>
       <c r="K72" s="33" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L72" s="33">
         <v>40</v>
       </c>
       <c r="M72" s="34" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="N72" s="34" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="O72" s="35">
         <v>1</v>
@@ -11954,22 +11954,22 @@
         <v>131</v>
       </c>
       <c r="H73" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I73" s="20" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="J73" s="20">
         <v>99</v>
       </c>
       <c r="K73" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L73" s="20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M73" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="N73" s="19"/>
       <c r="O73" s="18"/>
@@ -12063,34 +12063,34 @@
         <v>6</v>
       </c>
       <c r="D74" s="19" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="E74" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F74" s="19" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="G74" s="19" t="s">
         <v>72</v>
       </c>
       <c r="H74" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I74" s="20" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="J74" s="20">
         <v>4</v>
       </c>
       <c r="K74" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L74" s="20" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M74" s="19" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="N74" s="19"/>
       <c r="O74" s="18"/>
@@ -12184,37 +12184,37 @@
         <v>6</v>
       </c>
       <c r="D75" s="37" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E75" s="37" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F75" s="37" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="G75" s="37" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="H75" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I75" s="36" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="J75" s="36">
         <v>1</v>
       </c>
       <c r="K75" s="36" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L75" s="36" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="M75" s="37" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="N75" s="37" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O75" s="38"/>
       <c r="P75" s="36"/>
@@ -12307,34 +12307,34 @@
         <v>6</v>
       </c>
       <c r="D76" s="19" t="s">
+        <v>271</v>
+      </c>
+      <c r="E76" s="19" t="s">
+        <v>282</v>
+      </c>
+      <c r="F76" s="19" t="s">
         <v>272</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="F76" s="19" t="s">
-        <v>273</v>
       </c>
       <c r="G76" s="19" t="s">
         <v>112</v>
       </c>
       <c r="H76" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I76" s="20" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="J76" s="20">
         <v>3</v>
       </c>
       <c r="K76" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L76" s="20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M76" s="19" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="N76" s="19"/>
       <c r="O76" s="18"/>
@@ -12428,34 +12428,34 @@
         <v>6</v>
       </c>
       <c r="D77" s="19" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E77" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F77" s="19" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G77" s="19" t="s">
         <v>90</v>
       </c>
       <c r="H77" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I77" s="20" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="J77" s="20">
         <v>2</v>
       </c>
       <c r="K77" s="20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L77" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M77" s="19" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="N77" s="19"/>
       <c r="O77" s="18"/>
@@ -12549,34 +12549,34 @@
         <v>6</v>
       </c>
       <c r="D78" s="19" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E78" s="19" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F78" s="19" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="G78" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H78" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I78" s="20" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="J78" s="20">
         <v>1</v>
       </c>
       <c r="K78" s="20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L78" s="20" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="M78" s="19" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="N78" s="19"/>
       <c r="O78" s="18"/>
@@ -12670,37 +12670,37 @@
         <v>6</v>
       </c>
       <c r="D79" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="E79" s="34" t="s">
+        <v>242</v>
+      </c>
+      <c r="F79" s="34" t="s">
         <v>209</v>
-      </c>
-      <c r="E79" s="34" t="s">
-        <v>243</v>
-      </c>
-      <c r="F79" s="34" t="s">
-        <v>210</v>
       </c>
       <c r="G79" s="34" t="s">
         <v>72</v>
       </c>
       <c r="H79" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I79" s="33" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="J79" s="33">
         <v>4</v>
       </c>
       <c r="K79" s="33" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="L79" s="33" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M79" s="34" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="N79" s="34" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="O79" s="35">
         <v>1</v>
@@ -12795,28 +12795,28 @@
         <v>6</v>
       </c>
       <c r="D80" s="34" t="s">
+        <v>578</v>
+      </c>
+      <c r="E80" s="34" t="s">
+        <v>579</v>
+      </c>
+      <c r="F80" s="34" t="s">
         <v>580</v>
       </c>
-      <c r="E80" s="34" t="s">
+      <c r="G80" s="34" t="s">
+        <v>664</v>
+      </c>
+      <c r="H80" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="I80" s="33" t="s">
         <v>581</v>
       </c>
-      <c r="F80" s="34" t="s">
-        <v>582</v>
-      </c>
-      <c r="G80" s="34" t="s">
-        <v>666</v>
-      </c>
-      <c r="H80" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="I80" s="33" t="s">
-        <v>583</v>
-      </c>
       <c r="J80" s="33">
         <v>1</v>
       </c>
       <c r="K80" s="33" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L80" s="33" t="s">
         <v>105</v>
@@ -12825,7 +12825,7 @@
         <v>105</v>
       </c>
       <c r="N80" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O80" s="35">
         <v>1</v>
@@ -12922,37 +12922,37 @@
         <v>6</v>
       </c>
       <c r="D81" s="34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E81" s="34" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F81" s="34" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G81" s="34" t="s">
         <v>85</v>
       </c>
       <c r="H81" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I81" s="33" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="J81" s="33">
         <v>6</v>
       </c>
       <c r="K81" s="33" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L81" s="33" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M81" s="34" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N81" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O81" s="35">
         <v>1</v>
@@ -13047,28 +13047,28 @@
         <v>6</v>
       </c>
       <c r="D82" s="34" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E82" s="34" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F82" s="34" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G82" s="34" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H82" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I82" s="33" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="J82" s="33">
         <v>2</v>
       </c>
       <c r="K82" s="33" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="L82" s="33" t="s">
         <v>105</v>
@@ -13077,7 +13077,7 @@
         <v>105</v>
       </c>
       <c r="N82" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O82" s="35">
         <v>1</v>
@@ -13174,37 +13174,37 @@
         <v>6</v>
       </c>
       <c r="D83" s="34" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="E83" s="34" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="F83" s="34" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G83" s="34" t="s">
         <v>146</v>
       </c>
       <c r="H83" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I83" s="33" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="J83" s="33">
         <v>99</v>
       </c>
       <c r="K83" s="33" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L83" s="33" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="M83" s="34" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="N83" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O83" s="35">
         <v>1</v>
@@ -13299,37 +13299,37 @@
         <v>6</v>
       </c>
       <c r="D84" s="34" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="E84" s="34" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="F84" s="34" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="G84" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H84" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I84" s="33" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="J84" s="33">
         <v>2</v>
       </c>
       <c r="K84" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L84" s="33">
         <v>45</v>
       </c>
       <c r="M84" s="34" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="N84" s="34" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="O84" s="35">
         <v>1</v>
@@ -13424,37 +13424,37 @@
         <v>6</v>
       </c>
       <c r="D85" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E85" s="37" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F85" s="37" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G85" s="37" t="s">
         <v>72</v>
       </c>
       <c r="H85" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I85" s="36" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="J85" s="36">
         <v>4</v>
       </c>
       <c r="K85" s="36" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L85" s="36" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M85" s="37" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N85" s="37" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="O85" s="38"/>
       <c r="P85" s="36"/>
@@ -13544,37 +13544,37 @@
         <v>6</v>
       </c>
       <c r="D86" s="37" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="E86" s="37" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="F86" s="37" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="H86" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I86" s="36" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="J86" s="36">
         <v>1</v>
       </c>
       <c r="K86" s="36" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L86" s="36" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M86" s="37" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="N86" s="37" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="O86" s="38"/>
       <c r="P86" s="36"/>
@@ -13664,37 +13664,37 @@
         <v>6</v>
       </c>
       <c r="D87" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="E87" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="F87" s="34" t="s">
         <v>262</v>
-      </c>
-      <c r="E87" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="F87" s="34" t="s">
-        <v>263</v>
       </c>
       <c r="G87" s="34" t="s">
         <v>113</v>
       </c>
       <c r="H87" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I87" s="33" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J87" s="33">
         <v>5</v>
       </c>
       <c r="K87" s="33" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="L87" s="33" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="M87" s="34" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N87" s="34" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="O87" s="35">
         <v>1</v>
@@ -13789,29 +13789,29 @@
         <v>6</v>
       </c>
       <c r="D88" s="34" t="s">
+        <v>874</v>
+      </c>
+      <c r="E88" s="34" t="s">
+        <v>875</v>
+      </c>
+      <c r="F88" s="34" t="s">
         <v>876</v>
-      </c>
-      <c r="E88" s="34" t="s">
-        <v>877</v>
-      </c>
-      <c r="F88" s="34" t="s">
-        <v>878</v>
       </c>
       <c r="G88" s="34"/>
       <c r="H88" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I88" s="33" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="J88" s="33"/>
       <c r="K88" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L88" s="33"/>
       <c r="M88" s="34"/>
       <c r="N88" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O88" s="35">
         <v>1</v>
@@ -13908,37 +13908,37 @@
         <v>6</v>
       </c>
       <c r="D89" s="37" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="E89" s="37" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F89" s="37" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="G89" s="37" t="s">
         <v>102</v>
       </c>
       <c r="H89" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I89" s="36" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="J89" s="36">
         <v>5</v>
       </c>
       <c r="K89" s="36" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="L89" s="36" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M89" s="37" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N89" s="37" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="O89" s="38"/>
       <c r="P89" s="36"/>
@@ -14031,37 +14031,37 @@
         <v>6</v>
       </c>
       <c r="D90" s="34" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E90" s="34" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F90" s="34" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="G90" s="34" t="s">
         <v>110</v>
       </c>
       <c r="H90" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I90" s="33" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="J90" s="33">
         <v>1</v>
       </c>
       <c r="K90" s="33" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L90" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M90" s="34" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="N90" s="34" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="O90" s="35">
         <v>1</v>
@@ -14156,34 +14156,34 @@
         <v>7</v>
       </c>
       <c r="D91" s="19" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="E91" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F91" s="19" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G91" s="19" t="s">
         <v>102</v>
       </c>
       <c r="H91" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I91" s="20" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="J91" s="20">
         <v>5</v>
       </c>
       <c r="K91" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L91" s="20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M91" s="19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="N91" s="19"/>
       <c r="O91" s="18"/>
@@ -14277,37 +14277,37 @@
         <v>7</v>
       </c>
       <c r="D92" s="34" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E92" s="34" t="s">
         <v>40</v>
       </c>
       <c r="F92" s="34" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G92" s="34" t="s">
         <v>105</v>
       </c>
       <c r="H92" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I92" s="33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="J92" s="33">
         <v>1</v>
       </c>
       <c r="K92" s="33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L92" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M92" s="34" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="N92" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O92" s="35">
         <v>1</v>
@@ -14414,7 +14414,7 @@
         <v>113</v>
       </c>
       <c r="H93" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I93" s="33" t="s">
         <v>128</v>
@@ -14423,16 +14423,16 @@
         <v>5</v>
       </c>
       <c r="K93" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L93" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="M93" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="M93" s="34" t="s">
-        <v>313</v>
-      </c>
       <c r="N93" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O93" s="35">
         <v>1</v>
@@ -14535,31 +14535,31 @@
         <v>40</v>
       </c>
       <c r="F94" s="34" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G94" s="34" t="s">
         <v>84</v>
       </c>
       <c r="H94" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I94" s="33" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J94" s="33">
         <v>1</v>
       </c>
       <c r="K94" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L94" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="M94" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="M94" s="34" t="s">
-        <v>313</v>
-      </c>
       <c r="N94" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O94" s="35">
         <v>1</v>
@@ -14662,31 +14662,31 @@
         <v>40</v>
       </c>
       <c r="F95" s="34" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="G95" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H95" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I95" s="33" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="J95" s="33">
         <v>2</v>
       </c>
       <c r="K95" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L95" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="M95" s="34" t="s">
         <v>311</v>
       </c>
-      <c r="M95" s="34" t="s">
-        <v>313</v>
-      </c>
       <c r="N95" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O95" s="35">
         <v>1</v>
@@ -14783,37 +14783,37 @@
         <v>7</v>
       </c>
       <c r="D96" s="37" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E96" s="37" t="s">
         <v>40</v>
       </c>
       <c r="F96" s="37" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G96" s="37" t="s">
         <v>139</v>
       </c>
       <c r="H96" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I96" s="36" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="J96" s="36">
         <v>99</v>
       </c>
       <c r="K96" s="36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L96" s="36" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M96" s="37" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N96" s="37" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="O96" s="38"/>
       <c r="P96" s="36"/>
@@ -14903,37 +14903,37 @@
         <v>7</v>
       </c>
       <c r="D97" s="37" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="E97" s="37" t="s">
         <v>40</v>
       </c>
       <c r="F97" s="37" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G97" s="37" t="s">
         <v>90</v>
       </c>
       <c r="H97" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I97" s="36" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="J97" s="36">
         <v>2</v>
       </c>
       <c r="K97" s="36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L97" s="36" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M97" s="37" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="N97" s="37" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="O97" s="38"/>
       <c r="P97" s="36"/>
@@ -15023,37 +15023,37 @@
         <v>7</v>
       </c>
       <c r="D98" s="34" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="E98" s="34" t="s">
         <v>40</v>
       </c>
       <c r="F98" s="34" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="G98" s="34" t="s">
         <v>72</v>
       </c>
       <c r="H98" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I98" s="33" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="J98" s="33">
         <v>3</v>
       </c>
       <c r="K98" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L98" s="33">
         <v>28</v>
       </c>
       <c r="M98" s="34" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="N98" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O98" s="35">
         <v>1</v>
@@ -15148,37 +15148,37 @@
         <v>7</v>
       </c>
       <c r="D99" s="34" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="E99" s="34" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F99" s="34" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="G99" s="34" t="s">
         <v>84</v>
       </c>
       <c r="H99" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I99" s="33" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="J99" s="33">
         <v>1</v>
       </c>
       <c r="K99" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L99" s="33">
         <v>29</v>
       </c>
       <c r="M99" s="34" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N99" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O99" s="35">
         <v>1</v>
@@ -15273,34 +15273,34 @@
         <v>7</v>
       </c>
       <c r="D100" s="19" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="E100" s="19" t="s">
         <v>40</v>
       </c>
       <c r="F100" s="19" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="G100" s="19" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="H100" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I100" s="20" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="J100" s="20">
         <v>99</v>
       </c>
       <c r="K100" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L100" s="20" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M100" s="19" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="N100" s="19"/>
       <c r="O100" s="18"/>
@@ -15394,37 +15394,37 @@
         <v>7</v>
       </c>
       <c r="D101" s="37" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E101" s="37" t="s">
         <v>40</v>
       </c>
       <c r="F101" s="37" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G101" s="37" t="s">
         <v>72</v>
       </c>
       <c r="H101" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I101" s="36" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="J101" s="36">
         <v>3</v>
       </c>
       <c r="K101" s="36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L101" s="36">
         <v>30</v>
       </c>
       <c r="M101" s="37" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="N101" s="37" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="O101" s="38"/>
       <c r="P101" s="36"/>
@@ -15517,37 +15517,37 @@
         <v>7</v>
       </c>
       <c r="D102" s="37" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E102" s="37" t="s">
         <v>40</v>
       </c>
       <c r="F102" s="37" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H102" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I102" s="36" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="J102" s="36">
         <v>99</v>
       </c>
       <c r="K102" s="36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L102" s="36" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M102" s="37" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="N102" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O102" s="38"/>
       <c r="P102" s="36"/>
@@ -15640,37 +15640,37 @@
         <v>7</v>
       </c>
       <c r="D103" s="37" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E103" s="37" t="s">
         <v>40</v>
       </c>
       <c r="F103" s="37" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G103" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H103" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I103" s="36" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="J103" s="36">
         <v>1</v>
       </c>
       <c r="K103" s="36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L103" s="36" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M103" s="37" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="N103" s="37" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="O103" s="38"/>
       <c r="P103" s="36"/>
@@ -15760,37 +15760,37 @@
         <v>1</v>
       </c>
       <c r="D104" s="34" t="s">
+        <v>695</v>
+      </c>
+      <c r="E104" s="34" t="s">
+        <v>696</v>
+      </c>
+      <c r="F104" s="34" t="s">
         <v>697</v>
-      </c>
-      <c r="E104" s="34" t="s">
-        <v>698</v>
-      </c>
-      <c r="F104" s="34" t="s">
-        <v>699</v>
       </c>
       <c r="G104" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H104" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I104" s="33" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="J104" s="33">
         <v>2</v>
       </c>
       <c r="K104" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L104" s="33">
         <v>7</v>
       </c>
       <c r="M104" s="34" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="N104" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O104" s="35">
         <v>1</v>
@@ -15887,37 +15887,37 @@
         <v>1</v>
       </c>
       <c r="D105" s="34" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="E105" s="34" t="s">
         <v>69</v>
       </c>
       <c r="F105" s="34" t="s">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="G105" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H105" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I105" s="33" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="J105" s="33">
         <v>2</v>
       </c>
       <c r="K105" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L105" s="33">
         <v>5</v>
       </c>
       <c r="M105" s="34" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="N105" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O105" s="35">
         <v>1</v>
@@ -16014,37 +16014,37 @@
         <v>1</v>
       </c>
       <c r="D106" s="34" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E106" s="34" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F106" s="34" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G106" s="34" t="s">
         <v>84</v>
       </c>
       <c r="H106" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I106" s="33" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="J106" s="33">
         <v>1</v>
       </c>
       <c r="K106" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L106" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M106" s="34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N106" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O106" s="35">
         <v>1</v>
@@ -16141,37 +16141,37 @@
         <v>1</v>
       </c>
       <c r="D107" s="34" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="E107" s="34" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="F107" s="34" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="G107" s="34" t="s">
         <v>146</v>
       </c>
       <c r="H107" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I107" s="33" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="J107" s="33">
         <v>99</v>
       </c>
       <c r="K107" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L107" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M107" s="34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N107" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O107" s="35">
         <v>1</v>
@@ -16268,37 +16268,37 @@
         <v>1</v>
       </c>
       <c r="D108" s="34" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E108" s="34" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F108" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G108" s="34" t="s">
         <v>105</v>
       </c>
       <c r="H108" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I108" s="33" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="J108" s="33">
         <v>99</v>
       </c>
       <c r="K108" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L108" s="33">
         <v>9</v>
       </c>
       <c r="M108" s="34" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N108" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O108" s="35">
         <v>1</v>
@@ -16404,25 +16404,25 @@
         <v>34</v>
       </c>
       <c r="G109" s="19" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="H109" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I109" s="20" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="J109" s="20">
         <v>1</v>
       </c>
       <c r="K109" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L109" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M109" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N109" s="19"/>
       <c r="O109" s="18"/>
@@ -16522,13 +16522,13 @@
         <v>54</v>
       </c>
       <c r="F110" s="19" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="G110" s="19" t="s">
         <v>85</v>
       </c>
       <c r="H110" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I110" s="20" t="s">
         <v>133</v>
@@ -16537,13 +16537,13 @@
         <v>6</v>
       </c>
       <c r="K110" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L110" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M110" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N110" s="19"/>
       <c r="O110" s="18"/>
@@ -16643,28 +16643,28 @@
         <v>54</v>
       </c>
       <c r="F111" s="19" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="G111" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H111" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I111" s="20" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="J111" s="20">
         <v>1</v>
       </c>
       <c r="K111" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L111" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M111" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N111" s="19"/>
       <c r="O111" s="18"/>
@@ -16758,37 +16758,37 @@
         <v>1</v>
       </c>
       <c r="D112" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="E112" s="34" t="s">
+        <v>642</v>
+      </c>
+      <c r="F112" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="G112" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="E112" s="34" t="s">
-        <v>644</v>
-      </c>
-      <c r="F112" s="34" t="s">
-        <v>168</v>
-      </c>
-      <c r="G112" s="34" t="s">
+      <c r="H112" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="I112" s="33" t="s">
         <v>170</v>
-      </c>
-      <c r="H112" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="I112" s="33" t="s">
-        <v>171</v>
       </c>
       <c r="J112" s="33">
         <v>99</v>
       </c>
       <c r="K112" s="33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L112" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M112" s="34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N112" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O112" s="35">
         <v>1</v>
@@ -16889,13 +16889,13 @@
         <v>61</v>
       </c>
       <c r="F113" s="31" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="G113" s="31" t="s">
         <v>72</v>
       </c>
       <c r="H113" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I113" s="30" t="s">
         <v>138</v>
@@ -16904,13 +16904,13 @@
         <v>4</v>
       </c>
       <c r="K113" s="30" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L113" s="30" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M113" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N113" s="31"/>
       <c r="O113" s="32"/>
@@ -17012,28 +17012,28 @@
         <v>61</v>
       </c>
       <c r="F114" s="31" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G114" s="31" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="H114" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I114" s="30" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="J114" s="30">
         <v>99</v>
       </c>
       <c r="K114" s="30" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L114" s="30" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M114" s="31" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N114" s="31"/>
       <c r="O114" s="32"/>
@@ -17135,13 +17135,13 @@
         <v>54</v>
       </c>
       <c r="F115" s="19" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="G115" s="19" t="s">
         <v>108</v>
       </c>
       <c r="H115" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I115" s="20" t="s">
         <v>157</v>
@@ -17150,13 +17150,13 @@
         <v>7</v>
       </c>
       <c r="K115" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L115" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M115" s="19" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N115" s="19"/>
       <c r="O115" s="18"/>
@@ -17262,7 +17262,7 @@
         <v>90</v>
       </c>
       <c r="H116" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I116" s="33" t="s">
         <v>52</v>
@@ -17271,16 +17271,16 @@
         <v>2</v>
       </c>
       <c r="K116" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L116" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M116" s="34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="N116" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O116" s="35">
         <v>1</v>
@@ -17377,37 +17377,37 @@
         <v>1</v>
       </c>
       <c r="D117" s="34" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E117" s="34" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F117" s="34" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G117" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H117" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I117" s="33" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="J117" s="33">
         <v>2</v>
       </c>
       <c r="K117" s="33" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L117" s="33">
         <v>9</v>
       </c>
       <c r="M117" s="34" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="N117" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O117" s="35">
         <v>1</v>
@@ -17504,34 +17504,34 @@
         <v>2</v>
       </c>
       <c r="D118" s="19" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E118" s="19" t="s">
         <v>53</v>
       </c>
       <c r="F118" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="G118" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="H118" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="I118" s="20" t="s">
         <v>399</v>
-      </c>
-      <c r="G118" s="19" t="s">
-        <v>400</v>
-      </c>
-      <c r="H118" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="I118" s="20" t="s">
-        <v>401</v>
       </c>
       <c r="J118" s="20">
         <v>6</v>
       </c>
       <c r="K118" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L118" s="20">
         <v>20</v>
       </c>
       <c r="M118" s="19" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="N118" s="19"/>
       <c r="O118" s="18"/>
@@ -17631,13 +17631,13 @@
         <v>64</v>
       </c>
       <c r="F119" s="37" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="G119" s="37" t="s">
         <v>72</v>
       </c>
       <c r="H119" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I119" s="36" t="s">
         <v>65</v>
@@ -17646,16 +17646,16 @@
         <v>4</v>
       </c>
       <c r="K119" s="36" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L119" s="36" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M119" s="37" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="N119" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O119" s="38"/>
       <c r="P119" s="36"/>
@@ -17748,35 +17748,35 @@
         <v>2</v>
       </c>
       <c r="D120" s="34" t="s">
+        <v>832</v>
+      </c>
+      <c r="E120" s="34" t="s">
+        <v>763</v>
+      </c>
+      <c r="F120" s="34" t="s">
+        <v>833</v>
+      </c>
+      <c r="G120" s="34" t="s">
         <v>834</v>
       </c>
-      <c r="E120" s="34" t="s">
-        <v>765</v>
-      </c>
-      <c r="F120" s="34" t="s">
+      <c r="H120" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="I120" s="33" t="s">
         <v>835</v>
-      </c>
-      <c r="G120" s="34" t="s">
-        <v>836</v>
-      </c>
-      <c r="H120" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="I120" s="33" t="s">
-        <v>837</v>
       </c>
       <c r="J120" s="33"/>
       <c r="K120" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L120" s="33">
         <v>30</v>
       </c>
       <c r="M120" s="34" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="N120" s="34" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="O120" s="35">
         <v>1</v>
@@ -17871,34 +17871,34 @@
         <v>2</v>
       </c>
       <c r="D121" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="E121" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="F121" s="19" t="s">
         <v>411</v>
-      </c>
-      <c r="E121" s="19" t="s">
-        <v>412</v>
-      </c>
-      <c r="F121" s="19" t="s">
-        <v>413</v>
       </c>
       <c r="G121" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H121" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I121" s="20" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="J121" s="20">
         <v>1</v>
       </c>
       <c r="K121" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L121" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M121" s="19" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="N121" s="19"/>
       <c r="O121" s="18"/>
@@ -17992,37 +17992,37 @@
         <v>2</v>
       </c>
       <c r="D122" s="34" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E122" s="34" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F122" s="34" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G122" s="34" t="s">
         <v>162</v>
       </c>
       <c r="H122" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I122" s="33" t="s">
+        <v>734</v>
+      </c>
+      <c r="J122" s="33">
+        <v>1</v>
+      </c>
+      <c r="K122" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="L122" s="33" t="s">
+        <v>797</v>
+      </c>
+      <c r="M122" s="34" t="s">
         <v>736</v>
       </c>
-      <c r="J122" s="33">
-        <v>1</v>
-      </c>
-      <c r="K122" s="33" t="s">
-        <v>297</v>
-      </c>
-      <c r="L122" s="33" t="s">
-        <v>799</v>
-      </c>
-      <c r="M122" s="34" t="s">
-        <v>738</v>
-      </c>
       <c r="N122" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O122" s="35">
         <v>1</v>
@@ -18117,34 +18117,34 @@
         <v>2</v>
       </c>
       <c r="D123" s="19" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E123" s="19" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="F123" s="19" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G123" s="19" t="s">
         <v>72</v>
       </c>
       <c r="H123" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I123" s="20" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="J123" s="20">
         <v>4</v>
       </c>
       <c r="K123" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L123" s="20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M123" s="19" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="N123" s="19"/>
       <c r="O123" s="18"/>
@@ -18238,34 +18238,34 @@
         <v>2</v>
       </c>
       <c r="D124" s="19" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E124" s="19" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F124" s="19" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="G124" s="19" t="s">
         <v>72</v>
       </c>
       <c r="H124" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I124" s="20" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="J124" s="20">
         <v>4</v>
       </c>
       <c r="K124" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L124" s="20" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M124" s="19" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="N124" s="19"/>
       <c r="O124" s="18"/>
@@ -18359,34 +18359,34 @@
         <v>2</v>
       </c>
       <c r="D125" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E125" s="19" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F125" s="19" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G125" s="19" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="H125" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I125" s="20" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="J125" s="20">
         <v>99</v>
       </c>
       <c r="K125" s="20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L125" s="20" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M125" s="19" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="N125" s="19"/>
       <c r="O125" s="18"/>
@@ -18480,34 +18480,34 @@
         <v>2</v>
       </c>
       <c r="D126" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="E126" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="F126" s="19" t="s">
+        <v>909</v>
+      </c>
+      <c r="G126" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="E126" s="19" t="s">
-        <v>387</v>
-      </c>
-      <c r="F126" s="19" t="s">
-        <v>286</v>
-      </c>
-      <c r="G126" s="19" t="s">
+      <c r="H126" s="19" t="s">
+        <v>192</v>
+      </c>
+      <c r="I126" s="20" t="s">
         <v>207</v>
       </c>
-      <c r="H126" s="19" t="s">
-        <v>193</v>
-      </c>
-      <c r="I126" s="20" t="s">
-        <v>208</v>
-      </c>
       <c r="J126" s="20">
         <v>1</v>
       </c>
       <c r="K126" s="20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L126" s="20" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M126" s="19" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="N126" s="19"/>
       <c r="O126" s="18"/>
@@ -18601,34 +18601,34 @@
         <v>2</v>
       </c>
       <c r="D127" s="19" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E127" s="19" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="F127" s="19" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G127" s="19" t="s">
         <v>72</v>
       </c>
       <c r="H127" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I127" s="20" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="J127" s="20">
         <v>4</v>
       </c>
       <c r="K127" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L127" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M127" s="19" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="N127" s="19"/>
       <c r="O127" s="18"/>
@@ -18728,28 +18728,28 @@
         <v>44</v>
       </c>
       <c r="F128" s="19" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="G128" s="19" t="s">
         <v>72</v>
       </c>
       <c r="H128" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I128" s="20" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J128" s="20">
         <v>4</v>
       </c>
       <c r="K128" s="20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L128" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M128" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N128" s="19"/>
       <c r="O128" s="18"/>
@@ -18849,13 +18849,13 @@
         <v>44</v>
       </c>
       <c r="F129" s="19" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="G129" s="19" t="s">
         <v>104</v>
       </c>
       <c r="H129" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I129" s="20" t="s">
         <v>122</v>
@@ -18864,13 +18864,13 @@
         <v>2</v>
       </c>
       <c r="K129" s="20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L129" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M129" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="N129" s="19"/>
       <c r="O129" s="18"/>
@@ -18964,28 +18964,28 @@
         <v>2</v>
       </c>
       <c r="D130" s="19" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="E130" s="19"/>
       <c r="F130" s="19" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="G130" s="19"/>
       <c r="H130" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I130" s="20" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="J130" s="20"/>
       <c r="K130" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L130" s="15">
         <v>22</v>
       </c>
       <c r="M130" s="39" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="N130" s="39"/>
       <c r="O130" s="2"/>
@@ -19079,37 +19079,37 @@
         <v>2</v>
       </c>
       <c r="D131" s="37" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E131" s="37" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F131" s="37" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="G131" s="37" t="s">
         <v>102</v>
       </c>
       <c r="H131" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I131" s="36" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="J131" s="36">
         <v>5</v>
       </c>
       <c r="K131" s="36" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L131" s="36" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M131" s="37" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N131" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O131" s="38"/>
       <c r="P131" s="36"/>
@@ -19202,34 +19202,34 @@
         <v>2</v>
       </c>
       <c r="D132" s="19" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="E132" s="19" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="F132" s="19" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="G132" s="19" t="s">
         <v>72</v>
       </c>
       <c r="H132" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I132" s="20" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="J132" s="20">
         <v>4</v>
       </c>
       <c r="K132" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L132" s="20" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="M132" s="19" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="N132" s="19"/>
       <c r="O132" s="18"/>
@@ -19323,37 +19323,37 @@
         <v>2</v>
       </c>
       <c r="D133" s="37" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E133" s="37" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F133" s="37" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G133" s="37" t="s">
         <v>147</v>
       </c>
       <c r="H133" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I133" s="36" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="J133" s="36">
         <v>99</v>
       </c>
       <c r="K133" s="36" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L133" s="36" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="M133" s="37" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="N133" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O133" s="38"/>
       <c r="P133" s="36"/>
@@ -19458,7 +19458,7 @@
         <v>90</v>
       </c>
       <c r="H134" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I134" s="33" t="s">
         <v>119</v>
@@ -19467,16 +19467,16 @@
         <v>2</v>
       </c>
       <c r="K134" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L134" s="33" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="M134" s="34" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="N134" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O134" s="35">
         <v>1</v>
@@ -19573,28 +19573,28 @@
         <v>3</v>
       </c>
       <c r="D135" s="31" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E135" s="31" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="F135" s="31" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="G135" s="31" t="s">
         <v>109</v>
       </c>
       <c r="H135" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I135" s="30" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="J135" s="30">
         <v>1</v>
       </c>
       <c r="K135" s="30" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L135" s="30" t="s">
         <v>105</v>
@@ -19696,28 +19696,28 @@
         <v>3</v>
       </c>
       <c r="D136" s="34" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E136" s="34" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F136" s="34" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G136" s="34" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H136" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I136" s="33" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="J136" s="33">
         <v>1</v>
       </c>
       <c r="K136" s="33" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="L136" s="33" t="s">
         <v>105</v>
@@ -19726,7 +19726,7 @@
         <v>105</v>
       </c>
       <c r="N136" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O136" s="35">
         <v>1</v>
@@ -19823,28 +19823,28 @@
         <v>3</v>
       </c>
       <c r="D137" s="34" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="E137" s="34" t="s">
         <v>101</v>
       </c>
       <c r="F137" s="34" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G137" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H137" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I137" s="33" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="J137" s="33">
         <v>2</v>
       </c>
       <c r="K137" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L137" s="33" t="s">
         <v>105</v>
@@ -19853,7 +19853,7 @@
         <v>105</v>
       </c>
       <c r="N137" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O137" s="35">
         <v>1</v>
@@ -19950,33 +19950,33 @@
         <v>3</v>
       </c>
       <c r="D138" s="34" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="E138" s="34" t="s">
+        <v>889</v>
+      </c>
+      <c r="F138" s="34" t="s">
         <v>891</v>
-      </c>
-      <c r="F138" s="34" t="s">
-        <v>893</v>
       </c>
       <c r="G138" s="34" t="s">
         <v>139</v>
       </c>
       <c r="H138" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I138" s="33" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="J138" s="33">
         <v>1</v>
       </c>
       <c r="K138" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L138" s="33"/>
       <c r="M138" s="34"/>
       <c r="N138" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O138" s="35">
         <v>1</v>
@@ -20073,28 +20073,28 @@
         <v>3</v>
       </c>
       <c r="D139" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="E139" s="34" t="s">
+        <v>644</v>
+      </c>
+      <c r="F139" s="34" t="s">
         <v>574</v>
-      </c>
-      <c r="E139" s="34" t="s">
-        <v>646</v>
-      </c>
-      <c r="F139" s="34" t="s">
-        <v>576</v>
       </c>
       <c r="G139" s="34" t="s">
         <v>139</v>
       </c>
       <c r="H139" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I139" s="33" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="J139" s="33">
         <v>1</v>
       </c>
       <c r="K139" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L139" s="33" t="s">
         <v>105</v>
@@ -20103,7 +20103,7 @@
         <v>105</v>
       </c>
       <c r="N139" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O139" s="35">
         <v>1</v>
@@ -20212,7 +20212,7 @@
         <v>90</v>
       </c>
       <c r="H140" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I140" s="33" t="s">
         <v>46</v>
@@ -20221,16 +20221,16 @@
         <v>2</v>
       </c>
       <c r="K140" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L140" s="33" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M140" s="34" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="N140" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O140" s="35">
         <v>1</v>
@@ -20333,13 +20333,13 @@
         <v>88</v>
       </c>
       <c r="F141" s="31" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="G141" s="31" t="s">
         <v>90</v>
       </c>
       <c r="H141" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I141" s="30" t="s">
         <v>71</v>
@@ -20348,13 +20348,13 @@
         <v>2</v>
       </c>
       <c r="K141" s="30" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L141" s="30" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M141" s="31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N141" s="31"/>
       <c r="O141" s="32"/>
@@ -20450,34 +20450,34 @@
         <v>4</v>
       </c>
       <c r="D142" s="19" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E142" s="19" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F142" s="19" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="G142" s="19" t="s">
         <v>110</v>
       </c>
       <c r="H142" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I142" s="20" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="J142" s="20">
         <v>1</v>
       </c>
       <c r="K142" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L142" s="20" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="M142" s="19" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="N142" s="19"/>
       <c r="O142" s="18"/>
@@ -20571,37 +20571,37 @@
         <v>4</v>
       </c>
       <c r="D143" s="37" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E143" s="37" t="s">
         <v>37</v>
       </c>
       <c r="F143" s="37" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G143" s="37" t="s">
         <v>72</v>
       </c>
       <c r="H143" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I143" s="36" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J143" s="36">
         <v>3</v>
       </c>
       <c r="K143" s="36" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L143" s="36" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M143" s="37" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="N143" s="37" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O143" s="38"/>
       <c r="P143" s="36"/>
@@ -20694,34 +20694,34 @@
         <v>4</v>
       </c>
       <c r="D144" s="19" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E144" s="19" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F144" s="19" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G144" s="19" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="H144" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I144" s="20" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J144" s="20">
         <v>2</v>
       </c>
       <c r="K144" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L144" s="20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M144" s="19" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="N144" s="19"/>
       <c r="O144" s="18"/>
@@ -20815,34 +20815,34 @@
         <v>4</v>
       </c>
       <c r="D145" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="E145" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F145" s="19" t="s">
         <v>415</v>
-      </c>
-      <c r="E145" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="F145" s="19" t="s">
-        <v>417</v>
       </c>
       <c r="G145" s="19" t="s">
         <v>85</v>
       </c>
       <c r="H145" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I145" s="20" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="J145" s="20">
         <v>6</v>
       </c>
       <c r="K145" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L145" s="20">
         <v>8</v>
       </c>
       <c r="M145" s="19" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="N145" s="19"/>
       <c r="O145" s="18"/>
@@ -20936,37 +20936,37 @@
         <v>4</v>
       </c>
       <c r="D146" s="37" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="E146" s="37" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F146" s="37" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G146" s="37" t="s">
         <v>112</v>
       </c>
       <c r="H146" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I146" s="36" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="J146" s="36">
         <v>3</v>
       </c>
       <c r="K146" s="36" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L146" s="36" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M146" s="37" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="N146" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O146" s="38"/>
       <c r="P146" s="36"/>
@@ -21059,37 +21059,37 @@
         <v>4</v>
       </c>
       <c r="D147" s="37" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E147" s="37" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F147" s="37" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="G147" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H147" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I147" s="36" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="J147" s="36">
         <v>1</v>
       </c>
       <c r="K147" s="36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L147" s="36" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M147" s="37" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="N147" s="37" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="O147" s="38"/>
       <c r="P147" s="36"/>
@@ -21182,34 +21182,34 @@
         <v>4</v>
       </c>
       <c r="D148" s="19" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E148" s="19" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F148" s="19" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="G148" s="19" t="s">
         <v>90</v>
       </c>
       <c r="H148" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I148" s="20" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J148" s="20">
         <v>2</v>
       </c>
       <c r="K148" s="20" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L148" s="20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M148" s="19" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="N148" s="19"/>
       <c r="O148" s="18"/>
@@ -21303,34 +21303,34 @@
         <v>4</v>
       </c>
       <c r="D149" s="19" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E149" s="19" t="s">
         <v>30</v>
       </c>
       <c r="F149" s="19" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="G149" s="19" t="s">
         <v>103</v>
       </c>
       <c r="H149" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I149" s="20" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J149" s="20">
         <v>7</v>
       </c>
       <c r="K149" s="20" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L149" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M149" s="19" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="N149" s="19"/>
       <c r="O149" s="18"/>
@@ -21424,34 +21424,34 @@
         <v>4</v>
       </c>
       <c r="D150" s="19" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="E150" s="19" t="s">
         <v>30</v>
       </c>
       <c r="F150" s="19" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="G150" s="19" t="s">
         <v>72</v>
       </c>
       <c r="H150" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I150" s="20" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="J150" s="20">
         <v>4</v>
       </c>
       <c r="K150" s="20" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L150" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M150" s="19" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="N150" s="19"/>
       <c r="O150" s="18"/>
@@ -21545,34 +21545,34 @@
         <v>4</v>
       </c>
       <c r="D151" s="19" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="E151" s="19" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="F151" s="19" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="G151" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H151" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I151" s="20" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="J151" s="20">
         <v>1</v>
       </c>
       <c r="K151" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L151" s="20">
         <v>15</v>
       </c>
       <c r="M151" s="19" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N151" s="19"/>
       <c r="O151" s="18"/>
@@ -21666,37 +21666,37 @@
         <v>4</v>
       </c>
       <c r="D152" s="41" t="s">
+        <v>469</v>
+      </c>
+      <c r="E152" s="41" t="s">
+        <v>470</v>
+      </c>
+      <c r="F152" s="41" t="s">
         <v>471</v>
-      </c>
-      <c r="E152" s="41" t="s">
-        <v>472</v>
-      </c>
-      <c r="F152" s="41" t="s">
-        <v>473</v>
       </c>
       <c r="G152" s="41" t="s">
         <v>90</v>
       </c>
       <c r="H152" s="41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I152" s="40" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="J152" s="40">
         <v>2</v>
       </c>
       <c r="K152" s="40" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L152" s="40" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M152" s="41" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="N152" s="41" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="O152" s="42"/>
       <c r="P152" s="40"/>
@@ -21786,30 +21786,30 @@
         <v>4</v>
       </c>
       <c r="D153" s="19" t="s">
+        <v>584</v>
+      </c>
+      <c r="E153" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="F153" s="19" t="s">
         <v>586</v>
-      </c>
-      <c r="E153" s="19" t="s">
-        <v>416</v>
-      </c>
-      <c r="F153" s="19" t="s">
-        <v>588</v>
       </c>
       <c r="G153" s="19"/>
       <c r="H153" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I153" s="20" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="J153" s="20"/>
       <c r="K153" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L153" s="20">
         <v>20</v>
       </c>
       <c r="M153" s="19" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="N153" s="19"/>
       <c r="O153" s="18"/>
@@ -21903,34 +21903,34 @@
         <v>5</v>
       </c>
       <c r="D154" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E154" s="19" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F154" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G154" s="19" t="s">
         <v>109</v>
       </c>
       <c r="H154" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I154" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="J154" s="20">
         <v>99</v>
       </c>
       <c r="K154" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L154" s="20">
         <v>30</v>
       </c>
       <c r="M154" s="19" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="N154" s="19"/>
       <c r="O154" s="18"/>
@@ -22024,35 +22024,35 @@
         <v>5</v>
       </c>
       <c r="D155" s="34" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="E155" s="34" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="F155" s="34" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G155" s="34" t="s">
         <v>84</v>
       </c>
       <c r="H155" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I155" s="33" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="J155" s="33"/>
       <c r="K155" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L155" s="33">
         <v>40</v>
       </c>
       <c r="M155" s="34" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="N155" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O155" s="35">
         <v>1</v>
@@ -22147,37 +22147,37 @@
         <v>5</v>
       </c>
       <c r="D156" s="34" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="E156" s="34" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F156" s="34" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G156" s="34" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="H156" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I156" s="33" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="J156" s="33">
         <v>2</v>
       </c>
       <c r="K156" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L156" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M156" s="34" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="N156" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O156" s="35">
         <v>1</v>
@@ -22272,34 +22272,34 @@
         <v>5</v>
       </c>
       <c r="D157" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="E157" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="F157" s="19" t="s">
         <v>535</v>
-      </c>
-      <c r="E157" s="19" t="s">
-        <v>536</v>
-      </c>
-      <c r="F157" s="19" t="s">
-        <v>537</v>
       </c>
       <c r="G157" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H157" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I157" s="20" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="J157" s="20">
         <v>1</v>
       </c>
       <c r="K157" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L157" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M157" s="19" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N157" s="19"/>
       <c r="O157" s="18"/>
@@ -22393,37 +22393,37 @@
         <v>5</v>
       </c>
       <c r="D158" s="37" t="s">
+        <v>851</v>
+      </c>
+      <c r="E158" s="37" t="s">
+        <v>852</v>
+      </c>
+      <c r="F158" s="37" t="s">
         <v>853</v>
-      </c>
-      <c r="E158" s="37" t="s">
-        <v>854</v>
-      </c>
-      <c r="F158" s="37" t="s">
-        <v>855</v>
       </c>
       <c r="G158" s="37" t="s">
         <v>131</v>
       </c>
       <c r="H158" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I158" s="36" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="J158" s="36">
         <v>99</v>
       </c>
       <c r="K158" s="36" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L158" s="36">
         <v>40</v>
       </c>
       <c r="M158" s="37" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="N158" s="37" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="O158" s="38"/>
       <c r="P158" s="36"/>
@@ -22516,33 +22516,33 @@
         <v>5</v>
       </c>
       <c r="D159" s="34" t="s">
+        <v>839</v>
+      </c>
+      <c r="E159" s="34" t="s">
+        <v>843</v>
+      </c>
+      <c r="F159" s="34" t="s">
         <v>841</v>
-      </c>
-      <c r="E159" s="34" t="s">
-        <v>845</v>
-      </c>
-      <c r="F159" s="34" t="s">
-        <v>843</v>
       </c>
       <c r="G159" s="34"/>
       <c r="H159" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I159" s="33" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="J159" s="33"/>
       <c r="K159" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L159" s="33">
         <v>35</v>
       </c>
       <c r="M159" s="34" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="N159" s="34" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="O159" s="35">
         <v>1</v>
@@ -22637,37 +22637,37 @@
         <v>5</v>
       </c>
       <c r="D160" s="34" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E160" s="34" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F160" s="34" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="G160" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H160" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I160" s="33" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="J160" s="33">
         <v>2</v>
       </c>
       <c r="K160" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L160" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M160" s="34" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="N160" s="34" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="O160" s="35">
         <v>1</v>
@@ -22762,33 +22762,33 @@
         <v>5</v>
       </c>
       <c r="D161" s="37" t="s">
+        <v>878</v>
+      </c>
+      <c r="E161" s="37" t="s">
+        <v>879</v>
+      </c>
+      <c r="F161" s="37" t="s">
         <v>880</v>
-      </c>
-      <c r="E161" s="37" t="s">
-        <v>881</v>
-      </c>
-      <c r="F161" s="37" t="s">
-        <v>882</v>
       </c>
       <c r="G161" s="37"/>
       <c r="H161" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I161" s="36" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="J161" s="36"/>
       <c r="K161" s="36" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L161" s="36">
         <v>35</v>
       </c>
       <c r="M161" s="37" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="N161" s="37" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="O161" s="38"/>
       <c r="P161" s="36"/>
@@ -22878,34 +22878,34 @@
         <v>6</v>
       </c>
       <c r="D162" s="19" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="E162" s="19" t="s">
         <v>50</v>
       </c>
       <c r="F162" s="19" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="G162" s="19" t="s">
         <v>72</v>
       </c>
       <c r="H162" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I162" s="20" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="J162" s="20">
         <v>4</v>
       </c>
       <c r="K162" s="20" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L162" s="20" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="M162" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="N162" s="19"/>
       <c r="O162" s="18"/>
@@ -23011,7 +23011,7 @@
         <v>84</v>
       </c>
       <c r="H163" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I163" s="20" t="s">
         <v>87</v>
@@ -23020,13 +23020,13 @@
         <v>1</v>
       </c>
       <c r="K163" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L163" s="20" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M163" s="19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N163" s="19"/>
       <c r="O163" s="18"/>
@@ -23126,13 +23126,13 @@
         <v>50</v>
       </c>
       <c r="F164" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G164" s="19" t="s">
         <v>103</v>
       </c>
       <c r="H164" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I164" s="20" t="s">
         <v>74</v>
@@ -23141,13 +23141,13 @@
         <v>7</v>
       </c>
       <c r="K164" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L164" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M164" s="19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N164" s="19"/>
       <c r="O164" s="18"/>
@@ -23241,37 +23241,37 @@
         <v>6</v>
       </c>
       <c r="D165" s="34" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="E165" s="34" t="s">
         <v>50</v>
       </c>
       <c r="F165" s="34" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="G165" s="34" t="s">
         <v>72</v>
       </c>
       <c r="H165" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I165" s="33" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="J165" s="33">
         <v>4</v>
       </c>
       <c r="K165" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L165" s="33" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="M165" s="34" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="N165" s="34" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="O165" s="35">
         <v>1</v>
@@ -23366,34 +23366,34 @@
         <v>6</v>
       </c>
       <c r="D166" s="19" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E166" s="19" t="s">
         <v>50</v>
       </c>
       <c r="F166" s="19" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="G166" s="19" t="s">
         <v>109</v>
       </c>
       <c r="H166" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I166" s="20" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="J166" s="20">
         <v>99</v>
       </c>
       <c r="K166" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L166" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M166" s="19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="N166" s="19"/>
       <c r="O166" s="18"/>
@@ -23499,16 +23499,16 @@
         <v>90</v>
       </c>
       <c r="H167" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I167" s="30" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="J167" s="30">
         <v>2</v>
       </c>
       <c r="K167" s="30" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L167" s="30" t="s">
         <v>105</v>
@@ -23616,13 +23616,13 @@
         <v>89</v>
       </c>
       <c r="F168" s="19" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="G168" s="19" t="s">
         <v>102</v>
       </c>
       <c r="H168" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I168" s="20" t="s">
         <v>156</v>
@@ -23631,13 +23631,13 @@
         <v>5</v>
       </c>
       <c r="K168" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L168" s="20">
         <v>20</v>
       </c>
       <c r="M168" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="N168" s="19"/>
       <c r="O168" s="18"/>
@@ -23731,37 +23731,37 @@
         <v>7</v>
       </c>
       <c r="D169" s="34" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E169" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F169" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G169" s="34" t="s">
         <v>84</v>
       </c>
       <c r="H169" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I169" s="33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="J169" s="33">
         <v>1</v>
       </c>
       <c r="K169" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L169" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M169" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N169" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O169" s="35">
         <v>1</v>
@@ -23858,19 +23858,19 @@
         <v>7</v>
       </c>
       <c r="D170" s="34" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E170" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F170" s="34" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="G170" s="34" t="s">
         <v>84</v>
       </c>
       <c r="H170" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I170" s="33" t="s">
         <v>47</v>
@@ -23879,16 +23879,16 @@
         <v>1</v>
       </c>
       <c r="K170" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L170" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M170" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N170" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O170" s="35">
         <v>1</v>
@@ -23985,19 +23985,19 @@
         <v>7</v>
       </c>
       <c r="D171" s="34" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E171" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F171" s="34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G171" s="34" t="s">
         <v>84</v>
       </c>
       <c r="H171" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I171" s="33" t="s">
         <v>48</v>
@@ -24006,16 +24006,16 @@
         <v>1</v>
       </c>
       <c r="K171" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L171" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M171" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N171" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O171" s="35">
         <v>1</v>
@@ -24112,37 +24112,37 @@
         <v>7</v>
       </c>
       <c r="D172" s="34" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E172" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F172" s="34" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="G172" s="34" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="H172" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I172" s="33" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="J172" s="33">
         <v>1</v>
       </c>
       <c r="K172" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L172" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M172" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N172" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O172" s="35">
         <v>1</v>
@@ -24239,37 +24239,37 @@
         <v>7</v>
       </c>
       <c r="D173" s="34" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E173" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F173" s="34" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G173" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H173" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I173" s="33" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="J173" s="33">
         <v>2</v>
       </c>
       <c r="K173" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L173" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M173" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N173" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O173" s="35">
         <v>1</v>
@@ -24366,37 +24366,37 @@
         <v>7</v>
       </c>
       <c r="D174" s="37" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E174" s="37" t="s">
         <v>38</v>
       </c>
       <c r="F174" s="37" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="G174" s="37" t="s">
         <v>112</v>
       </c>
       <c r="H174" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I174" s="36" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="J174" s="36">
         <v>3</v>
       </c>
       <c r="K174" s="36" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L174" s="36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M174" s="37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N174" s="37" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="O174" s="38"/>
       <c r="P174" s="36"/>
@@ -24489,37 +24489,37 @@
         <v>7</v>
       </c>
       <c r="D175" s="37" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E175" s="37" t="s">
         <v>38</v>
       </c>
       <c r="F175" s="37" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G175" s="37" t="s">
         <v>147</v>
       </c>
       <c r="H175" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I175" s="36" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="J175" s="36">
         <v>99</v>
       </c>
       <c r="K175" s="36" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L175" s="36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M175" s="37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N175" s="37" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="O175" s="38"/>
       <c r="P175" s="36"/>
@@ -24612,34 +24612,34 @@
         <v>7</v>
       </c>
       <c r="D176" s="19" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E176" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F176" s="19" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="G176" s="19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H176" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I176" s="20" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="J176" s="20">
         <v>99</v>
       </c>
       <c r="K176" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L176" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M176" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N176" s="19"/>
       <c r="O176" s="18"/>
@@ -24739,28 +24739,28 @@
         <v>38</v>
       </c>
       <c r="F177" s="19" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G177" s="19" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H177" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I177" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J177" s="20">
         <v>3</v>
       </c>
       <c r="K177" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L177" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M177" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N177" s="19"/>
       <c r="O177" s="18"/>
@@ -24860,28 +24860,28 @@
         <v>38</v>
       </c>
       <c r="F178" s="19" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G178" s="19" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="H178" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I178" s="20" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="J178" s="20">
         <v>99</v>
       </c>
       <c r="K178" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L178" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M178" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N178" s="19"/>
       <c r="O178" s="18"/>
@@ -24975,7 +24975,7 @@
         <v>7</v>
       </c>
       <c r="D179" s="19" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="E179" s="19" t="s">
         <v>38</v>
@@ -24987,7 +24987,7 @@
         <v>84</v>
       </c>
       <c r="H179" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I179" s="20" t="s">
         <v>78</v>
@@ -24996,13 +24996,13 @@
         <v>1</v>
       </c>
       <c r="K179" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L179" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M179" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N179" s="19"/>
       <c r="O179" s="18"/>
@@ -25096,34 +25096,34 @@
         <v>7</v>
       </c>
       <c r="D180" s="19" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E180" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F180" s="19" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="G180" s="19" t="s">
         <v>147</v>
       </c>
       <c r="H180" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I180" s="20" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="J180" s="20">
         <v>99</v>
       </c>
       <c r="K180" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L180" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M180" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N180" s="19"/>
       <c r="O180" s="18"/>
@@ -25217,19 +25217,19 @@
         <v>7</v>
       </c>
       <c r="D181" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E181" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F181" s="19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G181" s="19" t="s">
         <v>112</v>
       </c>
       <c r="H181" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I181" s="20" t="s">
         <v>120</v>
@@ -25238,13 +25238,13 @@
         <v>3</v>
       </c>
       <c r="K181" s="20" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L181" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M181" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N181" s="19"/>
       <c r="O181" s="18"/>
@@ -25338,19 +25338,19 @@
         <v>7</v>
       </c>
       <c r="D182" s="19" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E182" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F182" s="19" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="G182" s="19" t="s">
         <v>103</v>
       </c>
       <c r="H182" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I182" s="20" t="s">
         <v>120</v>
@@ -25359,13 +25359,13 @@
         <v>7</v>
       </c>
       <c r="K182" s="20" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L182" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M182" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N182" s="19"/>
       <c r="O182" s="18"/>
@@ -25459,19 +25459,19 @@
         <v>7</v>
       </c>
       <c r="D183" s="34" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E183" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F183" s="34" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="G183" s="34" t="s">
         <v>146</v>
       </c>
       <c r="H183" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I183" s="33" t="s">
         <v>145</v>
@@ -25480,16 +25480,16 @@
         <v>99</v>
       </c>
       <c r="K183" s="33" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L183" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M183" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N183" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O183" s="35">
         <v>1</v>
@@ -25586,19 +25586,19 @@
         <v>7</v>
       </c>
       <c r="D184" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E184" s="37" t="s">
         <v>38</v>
       </c>
       <c r="F184" s="37" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G184" s="37" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H184" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I184" s="36" t="s">
         <v>141</v>
@@ -25607,16 +25607,16 @@
         <v>99</v>
       </c>
       <c r="K184" s="36" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L184" s="36">
         <v>4</v>
       </c>
       <c r="M184" s="37" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N184" s="37" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="O184" s="38"/>
       <c r="P184" s="36"/>
@@ -25706,7 +25706,7 @@
         <v>7</v>
       </c>
       <c r="D185" s="19" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E185" s="19" t="s">
         <v>38</v>
@@ -25718,7 +25718,7 @@
         <v>84</v>
       </c>
       <c r="H185" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I185" s="20" t="s">
         <v>159</v>
@@ -25727,13 +25727,13 @@
         <v>1</v>
       </c>
       <c r="K185" s="20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L185" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M185" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N185" s="19"/>
       <c r="O185" s="18"/>
@@ -25827,19 +25827,19 @@
         <v>7</v>
       </c>
       <c r="D186" s="19" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="E186" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F186" s="19" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="G186" s="19" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H186" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I186" s="20" t="s">
         <v>142</v>
@@ -25848,13 +25848,13 @@
         <v>99</v>
       </c>
       <c r="K186" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L186" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M186" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N186" s="19"/>
       <c r="O186" s="18"/>
@@ -25960,7 +25960,7 @@
         <v>90</v>
       </c>
       <c r="H187" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I187" s="30" t="s">
         <v>121</v>
@@ -25969,7 +25969,7 @@
         <v>2</v>
       </c>
       <c r="K187" s="30" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L187" s="30" t="s">
         <v>105</v>
@@ -26071,34 +26071,34 @@
         <v>7</v>
       </c>
       <c r="D188" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E188" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F188" s="19" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="G188" s="19" t="s">
         <v>110</v>
       </c>
       <c r="H188" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I188" s="20" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J188" s="20">
         <v>1</v>
       </c>
       <c r="K188" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L188" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M188" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N188" s="19"/>
       <c r="O188" s="18"/>
@@ -26192,34 +26192,34 @@
         <v>7</v>
       </c>
       <c r="D189" s="19" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="E189" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F189" s="19" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G189" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H189" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I189" s="20" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="J189" s="20">
         <v>1</v>
       </c>
       <c r="K189" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L189" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M189" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N189" s="19"/>
       <c r="O189" s="18"/>
@@ -26319,28 +26319,28 @@
         <v>99</v>
       </c>
       <c r="F190" s="19" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="G190" s="19" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="H190" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I190" s="20" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="J190" s="20">
         <v>99</v>
       </c>
       <c r="K190" s="20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L190" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M190" s="19" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N190" s="19"/>
       <c r="O190" s="18"/>
@@ -26446,7 +26446,7 @@
         <v>84</v>
       </c>
       <c r="H191" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I191" s="20" t="s">
         <v>35</v>
@@ -26455,13 +26455,13 @@
         <v>1</v>
       </c>
       <c r="K191" s="20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L191" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M191" s="19" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N191" s="19"/>
       <c r="O191" s="18"/>
@@ -26561,13 +26561,13 @@
         <v>99</v>
       </c>
       <c r="F192" s="19" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G192" s="19" t="s">
         <v>90</v>
       </c>
       <c r="H192" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I192" s="20" t="s">
         <v>36</v>
@@ -26576,13 +26576,13 @@
         <v>2</v>
       </c>
       <c r="K192" s="20" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L192" s="20" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="M192" s="19" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="N192" s="19"/>
       <c r="O192" s="18"/>
@@ -26676,19 +26676,19 @@
         <v>7</v>
       </c>
       <c r="D193" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E193" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F193" s="34" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G193" s="34" t="s">
         <v>72</v>
       </c>
       <c r="H193" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I193" s="33" t="s">
         <v>49</v>
@@ -26697,16 +26697,16 @@
         <v>4</v>
       </c>
       <c r="K193" s="33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L193" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M193" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N193" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O193" s="35">
         <v>1</v>
@@ -26803,37 +26803,37 @@
         <v>7</v>
       </c>
       <c r="D194" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E194" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F194" s="34" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G194" s="34" t="s">
         <v>85</v>
       </c>
       <c r="H194" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I194" s="33" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="J194" s="33">
         <v>6</v>
       </c>
       <c r="K194" s="33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L194" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M194" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N194" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O194" s="35">
         <v>1</v>
@@ -26930,37 +26930,37 @@
         <v>7</v>
       </c>
       <c r="D195" s="34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E195" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F195" s="34" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G195" s="34" t="s">
         <v>84</v>
       </c>
       <c r="H195" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I195" s="33" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J195" s="33">
         <v>1</v>
       </c>
       <c r="K195" s="33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L195" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M195" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N195" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O195" s="35">
         <v>1</v>
@@ -27057,34 +27057,34 @@
         <v>7</v>
       </c>
       <c r="D196" s="19" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E196" s="19" t="s">
         <v>55</v>
       </c>
       <c r="F196" s="19" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="G196" s="19" t="s">
         <v>112</v>
       </c>
       <c r="H196" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I196" s="20" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="J196" s="20">
         <v>3</v>
       </c>
       <c r="K196" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L196" s="20" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="M196" s="19" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="N196" s="19"/>
       <c r="O196" s="18"/>
@@ -27178,34 +27178,34 @@
         <v>7</v>
       </c>
       <c r="D197" s="19" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E197" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F197" s="19" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G197" s="19" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="H197" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I197" s="20" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="J197" s="20">
         <v>99</v>
       </c>
       <c r="K197" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L197" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M197" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N197" s="19"/>
       <c r="O197" s="18"/>
@@ -27299,34 +27299,34 @@
         <v>7</v>
       </c>
       <c r="D198" s="19" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E198" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F198" s="19" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G198" s="19" t="s">
         <v>108</v>
       </c>
       <c r="H198" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I198" s="20" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="J198" s="20">
         <v>7</v>
       </c>
       <c r="K198" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L198" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M198" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N198" s="19"/>
       <c r="O198" s="18"/>
@@ -27420,34 +27420,34 @@
         <v>7</v>
       </c>
       <c r="D199" s="19" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E199" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F199" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="G199" s="19" t="s">
         <v>328</v>
       </c>
-      <c r="G199" s="19" t="s">
-        <v>330</v>
-      </c>
       <c r="H199" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I199" s="20" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="J199" s="20">
         <v>99</v>
       </c>
       <c r="K199" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L199" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M199" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N199" s="19"/>
       <c r="O199" s="18"/>
@@ -27541,31 +27541,31 @@
         <v>7</v>
       </c>
       <c r="D200" s="19" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E200" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F200" s="19" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="G200" s="19" t="s">
         <v>72</v>
       </c>
       <c r="H200" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I200" s="20" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="J200" s="20">
         <v>4</v>
       </c>
       <c r="K200" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L200" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M200" s="19" t="s">
         <v>105</v>
@@ -27662,31 +27662,31 @@
         <v>7</v>
       </c>
       <c r="D201" s="19" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="E201" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F201" s="19" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G201" s="19" t="s">
         <v>102</v>
       </c>
       <c r="H201" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I201" s="20" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="J201" s="20">
         <v>99</v>
       </c>
       <c r="K201" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L201" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M201" s="19" t="s">
         <v>105</v>
@@ -27783,19 +27783,19 @@
         <v>7</v>
       </c>
       <c r="D202" s="34" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E202" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F202" s="34" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G202" s="34" t="s">
         <v>84</v>
       </c>
       <c r="H202" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I202" s="33" t="s">
         <v>82</v>
@@ -27804,16 +27804,16 @@
         <v>1</v>
       </c>
       <c r="K202" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L202" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M202" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N202" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O202" s="35">
         <v>1</v>
@@ -27908,7 +27908,7 @@
         <v>7</v>
       </c>
       <c r="D203" s="34" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E203" s="34" t="s">
         <v>38</v>
@@ -27920,7 +27920,7 @@
         <v>85</v>
       </c>
       <c r="H203" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I203" s="33" t="s">
         <v>83</v>
@@ -27929,16 +27929,16 @@
         <v>6</v>
       </c>
       <c r="K203" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L203" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M203" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N203" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O203" s="35">
         <v>1</v>
@@ -28039,28 +28039,28 @@
         <v>38</v>
       </c>
       <c r="F204" s="19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G204" s="19" t="s">
         <v>85</v>
       </c>
       <c r="H204" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I204" s="20" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="J204" s="20">
         <v>6</v>
       </c>
       <c r="K204" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L204" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M204" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N204" s="19"/>
       <c r="O204" s="18"/>
@@ -28160,28 +28160,28 @@
         <v>38</v>
       </c>
       <c r="F205" s="19" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="G205" s="19" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="H205" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I205" s="20" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="J205" s="20">
         <v>99</v>
       </c>
       <c r="K205" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L205" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M205" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N205" s="19"/>
       <c r="O205" s="18"/>
@@ -28275,37 +28275,37 @@
         <v>7</v>
       </c>
       <c r="D206" s="34" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E206" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F206" s="34" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G206" s="34" t="s">
         <v>72</v>
       </c>
       <c r="H206" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I206" s="33" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="J206" s="33">
         <v>4</v>
       </c>
       <c r="K206" s="33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L206" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M206" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N206" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O206" s="35">
         <v>1</v>
@@ -28400,37 +28400,37 @@
         <v>7</v>
       </c>
       <c r="D207" s="34" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="E207" s="34" t="s">
         <v>38</v>
       </c>
       <c r="F207" s="34" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="G207" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H207" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I207" s="33" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="J207" s="33">
         <v>2</v>
       </c>
       <c r="K207" s="33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L207" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M207" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N207" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="O207" s="35">
         <v>1</v>
@@ -28531,13 +28531,13 @@
         <v>38</v>
       </c>
       <c r="F208" s="34" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G208" s="34" t="s">
         <v>84</v>
       </c>
       <c r="H208" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I208" s="33" t="s">
         <v>161</v>
@@ -28546,16 +28546,16 @@
         <v>1</v>
       </c>
       <c r="K208" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L208" s="33" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M208" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N208" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O208" s="35">
         <v>1</v>
@@ -28652,28 +28652,28 @@
         <v>7</v>
       </c>
       <c r="D209" s="34" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="E209" s="34" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="F209" s="34" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="G209" s="34" t="s">
         <v>90</v>
       </c>
       <c r="H209" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I209" s="33" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="J209" s="33">
         <v>2</v>
       </c>
       <c r="K209" s="33" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="L209" s="33" t="s">
         <v>105</v>
@@ -28682,7 +28682,7 @@
         <v>105</v>
       </c>
       <c r="N209" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O209" s="35">
         <v>1</v>
@@ -28779,34 +28779,34 @@
         <v>7</v>
       </c>
       <c r="D210" s="19" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="E210" s="19" t="s">
         <v>38</v>
       </c>
       <c r="F210" s="19" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="G210" s="19" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="H210" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I210" s="20" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="J210" s="20">
         <v>1</v>
       </c>
       <c r="K210" s="20" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L210" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M210" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N210" s="19"/>
       <c r="O210" s="18"/>
@@ -28900,7 +28900,7 @@
         <v>7</v>
       </c>
       <c r="D211" s="19" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E211" s="19" t="s">
         <v>38</v>
@@ -28909,10 +28909,10 @@
         <v>143</v>
       </c>
       <c r="G211" s="19" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H211" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I211" s="20" t="s">
         <v>144</v>
@@ -28921,13 +28921,13 @@
         <v>99</v>
       </c>
       <c r="K211" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L211" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M211" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N211" s="19"/>
       <c r="O211" s="18"/>
@@ -29021,19 +29021,19 @@
         <v>7</v>
       </c>
       <c r="D212" s="31" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E212" s="31" t="s">
         <v>55</v>
       </c>
       <c r="F212" s="31" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="G212" s="31" t="s">
         <v>90</v>
       </c>
       <c r="H212" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I212" s="30" t="s">
         <v>56</v>
@@ -29042,7 +29042,7 @@
         <v>2</v>
       </c>
       <c r="K212" s="30" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L212" s="30" t="s">
         <v>105</v>
@@ -29144,28 +29144,28 @@
         <v>7</v>
       </c>
       <c r="D213" s="31" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="E213" s="31" t="s">
         <v>55</v>
       </c>
       <c r="F213" s="31" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="G213" s="31" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="H213" s="31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I213" s="30" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="J213" s="30">
         <v>1</v>
       </c>
       <c r="K213" s="30" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L213" s="30" t="s">
         <v>105</v>
@@ -29267,28 +29267,28 @@
         <v>7</v>
       </c>
       <c r="D214" s="34" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E214" s="34" t="s">
         <v>55</v>
       </c>
       <c r="F214" s="34" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="G214" s="34" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="H214" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I214" s="33" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="J214" s="33">
         <v>1</v>
       </c>
       <c r="K214" s="33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L214" s="33" t="s">
         <v>105</v>
@@ -29297,7 +29297,7 @@
         <v>105</v>
       </c>
       <c r="N214" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O214" s="35">
         <v>1</v>
@@ -29394,28 +29394,28 @@
         <v>7</v>
       </c>
       <c r="D215" s="34" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E215" s="34" t="s">
         <v>55</v>
       </c>
       <c r="F215" s="34" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="G215" s="34" t="s">
         <v>147</v>
       </c>
       <c r="H215" s="34" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I215" s="33" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="J215" s="33">
         <v>99</v>
       </c>
       <c r="K215" s="33" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="L215" s="33" t="s">
         <v>105</v>
@@ -29424,7 +29424,7 @@
         <v>105</v>
       </c>
       <c r="N215" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="O215" s="35">
         <v>1</v>
@@ -29518,37 +29518,37 @@
         <v>7</v>
       </c>
       <c r="D216" s="37" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="E216" s="37" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F216" s="37" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="G216" s="37" t="s">
         <v>84</v>
       </c>
       <c r="H216" s="37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I216" s="36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="J216" s="36">
         <v>1</v>
       </c>
       <c r="K216" s="36" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L216" s="36" t="s">
+        <v>312</v>
+      </c>
+      <c r="M216" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="M216" s="37" t="s">
-        <v>316</v>
-      </c>
       <c r="N216" s="37" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="O216" s="38"/>
       <c r="P216" s="36"/>
@@ -29644,13 +29644,13 @@
         <v>38</v>
       </c>
       <c r="F217" s="19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G217" s="19" t="s">
         <v>84</v>
       </c>
       <c r="H217" s="19" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I217" s="20" t="s">
         <v>62</v>
@@ -29659,13 +29659,13 @@
         <v>1</v>
       </c>
       <c r="K217" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="L217" s="20" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M217" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N217" s="19"/>
       <c r="O217" s="18"/>
